--- a/research/traditional_assets/database/data/papua_new_guinea/papua_new_guinea_diversified.xlsx
+++ b/research/traditional_assets/database/data/papua_new_guinea/papua_new_guinea_diversified.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1308135545170994</v>
+        <v>0.130452613853548</v>
       </c>
       <c r="C2">
-        <v>377.4689989509737</v>
+        <v>375.3079947404788</v>
       </c>
       <c r="D2">
-        <v>369.3889989509738</v>
+        <v>370.9639947404788</v>
       </c>
       <c r="E2">
-        <v>-108.8</v>
+        <v>-105.064</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>3.736</v>
       </c>
       <c r="G2">
         <v>8.08</v>
@@ -1451,28 +1451,28 @@
         <v>28.275</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.1879208</v>
       </c>
       <c r="N2">
-        <v>28.275</v>
+        <v>28.0870792</v>
       </c>
       <c r="O2">
-        <v>8.4825</v>
+        <v>8.426123759999999</v>
       </c>
       <c r="P2">
-        <v>19.7925</v>
+        <v>19.66095544</v>
       </c>
       <c r="Q2">
-        <v>47.8925</v>
+        <v>47.76095544</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1308135545170994</v>
+        <v>0.1314146604581293</v>
       </c>
       <c r="T2">
-        <v>0.7282077218429368</v>
+        <v>0.7333566653307151</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>150.4623224251919</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.130452613853548</v>
+        <v>0.1300916731899967</v>
       </c>
       <c r="C3">
-        <v>375.3079947404788</v>
+        <v>373.1604789329026</v>
       </c>
       <c r="D3">
-        <v>370.9639947404788</v>
+        <v>372.5524789329026</v>
       </c>
       <c r="E3">
-        <v>-105.064</v>
+        <v>-101.328</v>
       </c>
       <c r="F3">
-        <v>3.736</v>
+        <v>7.472</v>
       </c>
       <c r="G3">
         <v>8.08</v>
@@ -1533,28 +1533,28 @@
         <v>28.275</v>
       </c>
       <c r="M3">
-        <v>0.1879208</v>
+        <v>0.3758416</v>
       </c>
       <c r="N3">
-        <v>28.0870792</v>
+        <v>27.8991584</v>
       </c>
       <c r="O3">
-        <v>8.426123759999999</v>
+        <v>8.369747519999999</v>
       </c>
       <c r="P3">
-        <v>19.66095544</v>
+        <v>19.52941088</v>
       </c>
       <c r="Q3">
-        <v>47.76095544</v>
+        <v>47.62941088</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1314146604581293</v>
+        <v>0.1320280338673436</v>
       </c>
       <c r="T3">
-        <v>0.7333566653307151</v>
+        <v>0.7386106892978359</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>150.4623224251919</v>
+        <v>75.23116121259594</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1300916731899967</v>
+        <v>0.1297307325264455</v>
       </c>
       <c r="C4">
-        <v>373.1604789329026</v>
+        <v>371.0266255472116</v>
       </c>
       <c r="D4">
-        <v>372.5524789329026</v>
+        <v>374.1546255472116</v>
       </c>
       <c r="E4">
-        <v>-101.328</v>
+        <v>-97.592</v>
       </c>
       <c r="F4">
-        <v>7.472</v>
+        <v>11.208</v>
       </c>
       <c r="G4">
         <v>8.08</v>
@@ -1615,28 +1615,28 @@
         <v>28.275</v>
       </c>
       <c r="M4">
-        <v>0.3758416</v>
+        <v>0.5637624</v>
       </c>
       <c r="N4">
-        <v>27.8991584</v>
+        <v>27.7112376</v>
       </c>
       <c r="O4">
-        <v>8.369747519999999</v>
+        <v>8.313371279999998</v>
       </c>
       <c r="P4">
-        <v>19.52941088</v>
+        <v>19.39786632</v>
       </c>
       <c r="Q4">
-        <v>47.62941088</v>
+        <v>47.49786632</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1320280338673436</v>
+        <v>0.1326540541509747</v>
       </c>
       <c r="T4">
-        <v>0.7386106892978359</v>
+        <v>0.7439730436560312</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>75.23116121259594</v>
+        <v>50.15410747506396</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1297307325264455</v>
+        <v>0.1293697918628941</v>
       </c>
       <c r="C5">
-        <v>371.0266255472116</v>
+        <v>368.9066116087464</v>
       </c>
       <c r="D5">
-        <v>374.1546255472116</v>
+        <v>375.7706116087464</v>
       </c>
       <c r="E5">
-        <v>-97.592</v>
+        <v>-93.85599999999999</v>
       </c>
       <c r="F5">
-        <v>11.208</v>
+        <v>14.944</v>
       </c>
       <c r="G5">
         <v>8.08</v>
@@ -1697,28 +1697,28 @@
         <v>28.275</v>
       </c>
       <c r="M5">
-        <v>0.5637624</v>
+        <v>0.7516832</v>
       </c>
       <c r="N5">
-        <v>27.7112376</v>
+        <v>27.5233168</v>
       </c>
       <c r="O5">
-        <v>8.313371279999998</v>
+        <v>8.25699504</v>
       </c>
       <c r="P5">
-        <v>19.39786632</v>
+        <v>19.26632176</v>
       </c>
       <c r="Q5">
-        <v>47.49786632</v>
+        <v>47.36632176000001</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1326540541509747</v>
+        <v>0.1332931165238481</v>
       </c>
       <c r="T5">
-        <v>0.7439730436560312</v>
+        <v>0.7494471137300224</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>50.15410747506396</v>
+        <v>37.61558060629797</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1293697918628941</v>
+        <v>0.1290088511993429</v>
       </c>
       <c r="C6">
-        <v>368.9066116087464</v>
+        <v>366.8006172144265</v>
       </c>
       <c r="D6">
-        <v>375.7706116087464</v>
+        <v>377.4006172144265</v>
       </c>
       <c r="E6">
-        <v>-93.85599999999999</v>
+        <v>-90.11999999999999</v>
       </c>
       <c r="F6">
-        <v>14.944</v>
+        <v>18.68</v>
       </c>
       <c r="G6">
         <v>8.08</v>
@@ -1779,28 +1779,28 @@
         <v>28.275</v>
       </c>
       <c r="M6">
-        <v>0.7516832</v>
+        <v>0.9396040000000001</v>
       </c>
       <c r="N6">
-        <v>27.5233168</v>
+        <v>27.335396</v>
       </c>
       <c r="O6">
-        <v>8.25699504</v>
+        <v>8.200618799999999</v>
       </c>
       <c r="P6">
-        <v>19.26632176</v>
+        <v>19.1347772</v>
       </c>
       <c r="Q6">
-        <v>47.36632176000001</v>
+        <v>47.2347772</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1332931165238481</v>
+        <v>0.1339456328414135</v>
       </c>
       <c r="T6">
-        <v>0.7494471137300224</v>
+        <v>0.7550364273845186</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>37.61558060629797</v>
+        <v>30.09246448503837</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1290088511993429</v>
+        <v>0.1286479105357915</v>
       </c>
       <c r="C7">
-        <v>366.8006172144265</v>
+        <v>364.7088255996604</v>
       </c>
       <c r="D7">
-        <v>377.4006172144265</v>
+        <v>379.0448255996604</v>
       </c>
       <c r="E7">
-        <v>-90.11999999999999</v>
+        <v>-86.38399999999999</v>
       </c>
       <c r="F7">
-        <v>18.68</v>
+        <v>22.416</v>
       </c>
       <c r="G7">
         <v>8.08</v>
@@ -1861,28 +1861,28 @@
         <v>28.275</v>
       </c>
       <c r="M7">
-        <v>0.9396040000000001</v>
+        <v>1.1275248</v>
       </c>
       <c r="N7">
-        <v>27.335396</v>
+        <v>27.1474752</v>
       </c>
       <c r="O7">
-        <v>8.200618799999999</v>
+        <v>8.144242559999999</v>
       </c>
       <c r="P7">
-        <v>19.1347772</v>
+        <v>19.00323264</v>
       </c>
       <c r="Q7">
-        <v>47.2347772</v>
+        <v>47.10323264</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1339456328414135</v>
+        <v>0.1346120324848846</v>
       </c>
       <c r="T7">
-        <v>0.7550364273845186</v>
+        <v>0.7607446626061318</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>30.09246448503837</v>
+        <v>25.07705373753198</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1286479105357915</v>
+        <v>0.1282869698722403</v>
       </c>
       <c r="C8">
-        <v>364.7088255996604</v>
+        <v>362.6314232070101</v>
       </c>
       <c r="D8">
-        <v>379.0448255996604</v>
+        <v>380.7034232070101</v>
       </c>
       <c r="E8">
-        <v>-86.384</v>
+        <v>-82.648</v>
       </c>
       <c r="F8">
-        <v>22.416</v>
+        <v>26.152</v>
       </c>
       <c r="G8">
         <v>8.08</v>
@@ -1943,28 +1943,28 @@
         <v>28.275</v>
       </c>
       <c r="M8">
-        <v>1.1275248</v>
+        <v>1.3154456</v>
       </c>
       <c r="N8">
-        <v>27.1474752</v>
+        <v>26.9595544</v>
       </c>
       <c r="O8">
-        <v>8.144242559999999</v>
+        <v>8.08786632</v>
       </c>
       <c r="P8">
-        <v>19.00323264</v>
+        <v>18.87168808</v>
       </c>
       <c r="Q8">
-        <v>47.10323264</v>
+        <v>46.97168808</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1346120324848846</v>
+        <v>0.1352927633034842</v>
       </c>
       <c r="T8">
-        <v>0.7607446626061318</v>
+        <v>0.7665756555744464</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>25.07705373753198</v>
+        <v>21.49461748931313</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1282869698722403</v>
+        <v>0.127926029208689</v>
       </c>
       <c r="C9">
-        <v>362.6314232070101</v>
+        <v>360.568599756669</v>
       </c>
       <c r="D9">
-        <v>380.7034232070101</v>
+        <v>382.376599756669</v>
       </c>
       <c r="E9">
-        <v>-82.648</v>
+        <v>-78.91199999999999</v>
       </c>
       <c r="F9">
-        <v>26.152</v>
+        <v>29.888</v>
       </c>
       <c r="G9">
         <v>8.08</v>
@@ -2025,28 +2025,28 @@
         <v>28.275</v>
       </c>
       <c r="M9">
-        <v>1.3154456</v>
+        <v>1.5033664</v>
       </c>
       <c r="N9">
-        <v>26.9595544</v>
+        <v>26.7716336</v>
       </c>
       <c r="O9">
-        <v>8.08786632</v>
+        <v>8.031490079999999</v>
       </c>
       <c r="P9">
-        <v>18.87168808</v>
+        <v>18.74014352</v>
       </c>
       <c r="Q9">
-        <v>46.97168808</v>
+        <v>46.84014352</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1352927633034842</v>
+        <v>0.1359882926181402</v>
       </c>
       <c r="T9">
-        <v>0.7665756555744464</v>
+        <v>0.7725334092594635</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>21.49461748931312</v>
+        <v>18.80779030314898</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.127926029208689</v>
+        <v>0.1275650885451377</v>
       </c>
       <c r="C10">
-        <v>360.568599756669</v>
+        <v>358.5205483188046</v>
       </c>
       <c r="D10">
-        <v>382.376599756669</v>
+        <v>384.0645483188046</v>
       </c>
       <c r="E10">
-        <v>-78.91199999999999</v>
+        <v>-75.17599999999999</v>
       </c>
       <c r="F10">
-        <v>29.888</v>
+        <v>33.624</v>
       </c>
       <c r="G10">
         <v>8.08</v>
@@ -2107,28 +2107,28 @@
         <v>28.275</v>
       </c>
       <c r="M10">
-        <v>1.5033664</v>
+        <v>1.6912872</v>
       </c>
       <c r="N10">
-        <v>26.7716336</v>
+        <v>26.5837128</v>
       </c>
       <c r="O10">
-        <v>8.031490079999999</v>
+        <v>7.975113839999999</v>
       </c>
       <c r="P10">
-        <v>18.74014352</v>
+        <v>18.60859896</v>
       </c>
       <c r="Q10">
-        <v>46.84014352</v>
+        <v>46.70859896</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1359882926181402</v>
+        <v>0.1366991082913601</v>
       </c>
       <c r="T10">
-        <v>0.7725334092594635</v>
+        <v>0.7786221025859094</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>18.80779030314898</v>
+        <v>16.71803582502132</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1275650885451377</v>
+        <v>0.1272041478815864</v>
       </c>
       <c r="C11">
-        <v>358.5205483188046</v>
+        <v>356.4874653878263</v>
       </c>
       <c r="D11">
-        <v>384.0645483188046</v>
+        <v>385.7674653878263</v>
       </c>
       <c r="E11">
-        <v>-75.17599999999999</v>
+        <v>-71.44</v>
       </c>
       <c r="F11">
-        <v>33.624</v>
+        <v>37.36</v>
       </c>
       <c r="G11">
         <v>8.08</v>
@@ -2189,28 +2189,28 @@
         <v>28.275</v>
       </c>
       <c r="M11">
-        <v>1.6912872</v>
+        <v>1.879208</v>
       </c>
       <c r="N11">
-        <v>26.5837128</v>
+        <v>26.395792</v>
       </c>
       <c r="O11">
-        <v>7.975113839999999</v>
+        <v>7.9187376</v>
       </c>
       <c r="P11">
-        <v>18.60859896</v>
+        <v>18.4770544</v>
       </c>
       <c r="Q11">
-        <v>46.70859896</v>
+        <v>46.5770544</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1366991082913601</v>
+        <v>0.1374257198684293</v>
       </c>
       <c r="T11">
-        <v>0.7786221025859094</v>
+        <v>0.7848461002084985</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>16.71803582502132</v>
+        <v>15.04623224251919</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1272041478815864</v>
+        <v>0.1268432072180351</v>
       </c>
       <c r="C12">
-        <v>356.4874653878263</v>
+        <v>354.4695509586378</v>
       </c>
       <c r="D12">
-        <v>385.7674653878263</v>
+        <v>387.4855509586378</v>
       </c>
       <c r="E12">
-        <v>-71.44</v>
+        <v>-67.70399999999999</v>
       </c>
       <c r="F12">
-        <v>37.36000000000001</v>
+        <v>41.096</v>
       </c>
       <c r="G12">
         <v>8.08</v>
@@ -2271,28 +2271,28 @@
         <v>28.275</v>
       </c>
       <c r="M12">
-        <v>1.879208</v>
+        <v>2.0671288</v>
       </c>
       <c r="N12">
-        <v>26.395792</v>
+        <v>26.2078712</v>
       </c>
       <c r="O12">
-        <v>7.9187376</v>
+        <v>7.86236136</v>
       </c>
       <c r="P12">
-        <v>18.4770544</v>
+        <v>18.34550984</v>
       </c>
       <c r="Q12">
-        <v>46.5770544</v>
+        <v>46.44550984</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1374257198684293</v>
+        <v>0.138168659795545</v>
       </c>
       <c r="T12">
-        <v>0.7848461002084985</v>
+        <v>0.7912099629462021</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>15.04623224251919</v>
+        <v>13.67839294774472</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1268432072180351</v>
+        <v>0.1266082665544838</v>
       </c>
       <c r="C13">
-        <v>354.4695509586378</v>
+        <v>351.8601202607695</v>
       </c>
       <c r="D13">
-        <v>387.4855509586378</v>
+        <v>388.6121202607695</v>
       </c>
       <c r="E13">
-        <v>-67.70399999999999</v>
+        <v>-63.968</v>
       </c>
       <c r="F13">
-        <v>41.096</v>
+        <v>44.832</v>
       </c>
       <c r="G13">
         <v>8.08</v>
@@ -2353,45 +2353,45 @@
         <v>28.275</v>
       </c>
       <c r="M13">
-        <v>2.0671288</v>
+        <v>2.3222976</v>
       </c>
       <c r="N13">
-        <v>26.2078712</v>
+        <v>25.9527024</v>
       </c>
       <c r="O13">
-        <v>7.86236136</v>
+        <v>7.78581072</v>
       </c>
       <c r="P13">
-        <v>18.34550984</v>
+        <v>18.16689168</v>
       </c>
       <c r="Q13">
-        <v>46.44550984</v>
+        <v>46.26689168</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.138168659795545</v>
+        <v>0.1389284847210043</v>
       </c>
       <c r="T13">
-        <v>0.7912099629462021</v>
+        <v>0.7977184589279445</v>
       </c>
       <c r="U13">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V13">
         <v>0.3</v>
       </c>
       <c r="W13">
-        <v>0.03521</v>
+        <v>0.03625999999999999</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y13">
-        <v>13.67839294774472</v>
+        <v>12.17544211387894</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1266082665544838</v>
+        <v>0.1262578258909325</v>
       </c>
       <c r="C14">
-        <v>351.8601202607695</v>
+        <v>349.8167522425592</v>
       </c>
       <c r="D14">
-        <v>388.6121202607695</v>
+        <v>390.3047522425592</v>
       </c>
       <c r="E14">
-        <v>-63.968</v>
+        <v>-60.23199999999999</v>
       </c>
       <c r="F14">
-        <v>44.832</v>
+        <v>48.568</v>
       </c>
       <c r="G14">
         <v>8.08</v>
@@ -2435,28 +2435,28 @@
         <v>28.275</v>
       </c>
       <c r="M14">
-        <v>2.3222976</v>
+        <v>2.5158224</v>
       </c>
       <c r="N14">
-        <v>25.9527024</v>
+        <v>25.7591776</v>
       </c>
       <c r="O14">
-        <v>7.78581072</v>
+        <v>7.727753279999999</v>
       </c>
       <c r="P14">
-        <v>18.16689168</v>
+        <v>18.03142432</v>
       </c>
       <c r="Q14">
-        <v>46.26689168</v>
+        <v>46.13142432</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1389284847210043</v>
+        <v>0.1397057768861293</v>
       </c>
       <c r="T14">
-        <v>0.7977184589279445</v>
+        <v>0.8043765755069681</v>
       </c>
       <c r="U14">
         <v>0.0518</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>12.17544211387894</v>
+        <v>11.23886964358056</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1262578258909325</v>
+        <v>0.1259073852273812</v>
       </c>
       <c r="C15">
-        <v>349.8167522425592</v>
+        <v>347.7881935224721</v>
       </c>
       <c r="D15">
-        <v>390.3047522425592</v>
+        <v>392.0121935224721</v>
       </c>
       <c r="E15">
-        <v>-60.23199999999999</v>
+        <v>-56.49599999999999</v>
       </c>
       <c r="F15">
-        <v>48.568</v>
+        <v>52.30400000000001</v>
       </c>
       <c r="G15">
         <v>8.08</v>
@@ -2517,28 +2517,28 @@
         <v>28.275</v>
       </c>
       <c r="M15">
-        <v>2.5158224</v>
+        <v>2.7093472</v>
       </c>
       <c r="N15">
-        <v>25.7591776</v>
+        <v>25.5656528</v>
       </c>
       <c r="O15">
-        <v>7.727753279999999</v>
+        <v>7.669695839999999</v>
       </c>
       <c r="P15">
-        <v>18.03142432</v>
+        <v>17.89595696</v>
       </c>
       <c r="Q15">
-        <v>46.13142432</v>
+        <v>45.99595696</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1397057768861293</v>
+        <v>0.1405011456132339</v>
       </c>
       <c r="T15">
-        <v>0.8043765755069681</v>
+        <v>0.8111895320064342</v>
       </c>
       <c r="U15">
         <v>0.0518</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>11.23886964358056</v>
+        <v>10.43609324046766</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1259073852273812</v>
+        <v>0.1257354445638299</v>
       </c>
       <c r="C16">
-        <v>347.7881935224721</v>
+        <v>344.8954094080187</v>
       </c>
       <c r="D16">
-        <v>392.0121935224721</v>
+        <v>392.8554094080187</v>
       </c>
       <c r="E16">
-        <v>-56.49599999999999</v>
+        <v>-52.75999999999998</v>
       </c>
       <c r="F16">
-        <v>52.30400000000001</v>
+        <v>56.04000000000001</v>
       </c>
       <c r="G16">
         <v>8.08</v>
@@ -2599,45 +2599,45 @@
         <v>28.275</v>
       </c>
       <c r="M16">
-        <v>2.7093472</v>
+        <v>2.998140000000001</v>
       </c>
       <c r="N16">
-        <v>25.5656528</v>
+        <v>25.27686</v>
       </c>
       <c r="O16">
-        <v>7.669695839999999</v>
+        <v>7.583057999999999</v>
       </c>
       <c r="P16">
-        <v>17.89595696</v>
+        <v>17.693802</v>
       </c>
       <c r="Q16">
-        <v>45.99595696</v>
+        <v>45.793802</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1405011456132339</v>
+        <v>0.1413152288986234</v>
       </c>
       <c r="T16">
-        <v>0.8111895320064342</v>
+        <v>0.8181627933647113</v>
       </c>
       <c r="U16">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V16">
         <v>0.3</v>
       </c>
       <c r="W16">
-        <v>0.03625999999999999</v>
+        <v>0.03745</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y16">
-        <v>10.43609324046766</v>
+        <v>9.430847125217634</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1257354445638299</v>
+        <v>0.1253969039002786</v>
       </c>
       <c r="C17">
-        <v>344.8954094080187</v>
+        <v>342.830297651955</v>
       </c>
       <c r="D17">
-        <v>392.8554094080187</v>
+        <v>394.5262976519551</v>
       </c>
       <c r="E17">
-        <v>-52.76</v>
+        <v>-49.02399999999999</v>
       </c>
       <c r="F17">
-        <v>56.04</v>
+        <v>59.776</v>
       </c>
       <c r="G17">
         <v>8.08</v>
@@ -2681,28 +2681,28 @@
         <v>28.275</v>
       </c>
       <c r="M17">
-        <v>2.99814</v>
+        <v>3.198016</v>
       </c>
       <c r="N17">
-        <v>25.27686</v>
+        <v>25.076984</v>
       </c>
       <c r="O17">
-        <v>7.583057999999999</v>
+        <v>7.523095199999999</v>
       </c>
       <c r="P17">
-        <v>17.693802</v>
+        <v>17.5538888</v>
       </c>
       <c r="Q17">
-        <v>45.793802</v>
+        <v>45.6538888</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1413152288986234</v>
+        <v>0.1421486951193793</v>
       </c>
       <c r="T17">
-        <v>0.8181627933647113</v>
+        <v>0.8253020847553284</v>
       </c>
       <c r="U17">
         <v>0.0535</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>9.430847125217635</v>
+        <v>8.841419179891533</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1253969039002786</v>
+        <v>0.1250583632367273</v>
       </c>
       <c r="C18">
-        <v>342.830297651955</v>
+        <v>340.7794598120239</v>
       </c>
       <c r="D18">
-        <v>394.5262976519551</v>
+        <v>396.2114598120239</v>
       </c>
       <c r="E18">
-        <v>-49.02399999999999</v>
+        <v>-45.28799999999999</v>
       </c>
       <c r="F18">
-        <v>59.776</v>
+        <v>63.51200000000001</v>
       </c>
       <c r="G18">
         <v>8.08</v>
@@ -2763,28 +2763,28 @@
         <v>28.275</v>
       </c>
       <c r="M18">
-        <v>3.198016</v>
+        <v>3.397892</v>
       </c>
       <c r="N18">
-        <v>25.076984</v>
+        <v>24.877108</v>
       </c>
       <c r="O18">
-        <v>7.523095199999999</v>
+        <v>7.463132399999999</v>
       </c>
       <c r="P18">
-        <v>17.5538888</v>
+        <v>17.4139756</v>
       </c>
       <c r="Q18">
-        <v>45.6538888</v>
+        <v>45.5139756</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1421486951193793</v>
+        <v>0.1430022448635269</v>
       </c>
       <c r="T18">
-        <v>0.8253020847553284</v>
+        <v>0.8326134072637916</v>
       </c>
       <c r="U18">
         <v>0.0535</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>8.841419179891533</v>
+        <v>8.321335698721441</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1250583632367273</v>
+        <v>0.124719822573176</v>
       </c>
       <c r="C19">
-        <v>340.7794598120239</v>
+        <v>338.7430795797575</v>
       </c>
       <c r="D19">
-        <v>396.2114598120239</v>
+        <v>397.9110795797575</v>
       </c>
       <c r="E19">
-        <v>-45.28799999999999</v>
+        <v>-41.55199999999998</v>
       </c>
       <c r="F19">
-        <v>63.51200000000001</v>
+        <v>67.24800000000002</v>
       </c>
       <c r="G19">
         <v>8.08</v>
@@ -2845,28 +2845,28 @@
         <v>28.275</v>
       </c>
       <c r="M19">
-        <v>3.397892</v>
+        <v>3.597768000000001</v>
       </c>
       <c r="N19">
-        <v>24.877108</v>
+        <v>24.677232</v>
       </c>
       <c r="O19">
-        <v>7.463132399999999</v>
+        <v>7.403169599999998</v>
       </c>
       <c r="P19">
-        <v>17.4139756</v>
+        <v>17.2740624</v>
       </c>
       <c r="Q19">
-        <v>45.5139756</v>
+        <v>45.3740624</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1430022448635269</v>
+        <v>0.143876612894117</v>
       </c>
       <c r="T19">
-        <v>0.8326134072637916</v>
+        <v>0.8401030547114856</v>
       </c>
       <c r="U19">
         <v>0.0535</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>8.321335698721441</v>
+        <v>7.859039271014693</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.124719822573176</v>
+        <v>0.1244876819096247</v>
       </c>
       <c r="C20">
-        <v>338.7430795797575</v>
+        <v>336.1809779563056</v>
       </c>
       <c r="D20">
-        <v>397.9110795797575</v>
+        <v>399.0849779563056</v>
       </c>
       <c r="E20">
-        <v>-41.55199999999999</v>
+        <v>-37.81599999999999</v>
       </c>
       <c r="F20">
-        <v>67.248</v>
+        <v>70.98400000000001</v>
       </c>
       <c r="G20">
         <v>8.08</v>
@@ -2927,45 +2927,45 @@
         <v>28.275</v>
       </c>
       <c r="M20">
-        <v>3.597768</v>
+        <v>3.854431200000001</v>
       </c>
       <c r="N20">
-        <v>24.677232</v>
+        <v>24.4205688</v>
       </c>
       <c r="O20">
-        <v>7.403169599999998</v>
+        <v>7.326170639999999</v>
       </c>
       <c r="P20">
-        <v>17.2740624</v>
+        <v>17.09439816</v>
       </c>
       <c r="Q20">
-        <v>45.3740624</v>
+        <v>45.19439816</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.143876612894117</v>
+        <v>0.1447725702587959</v>
       </c>
       <c r="T20">
-        <v>0.8401030547114856</v>
+        <v>0.8477776317257893</v>
       </c>
       <c r="U20">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V20">
         <v>0.3</v>
       </c>
       <c r="W20">
-        <v>0.03745</v>
+        <v>0.03801</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y20">
-        <v>7.859039271014694</v>
+        <v>7.335712724616799</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1244876819096247</v>
+        <v>0.1241547412460734</v>
       </c>
       <c r="C21">
-        <v>336.1809779563056</v>
+        <v>334.1407479283721</v>
       </c>
       <c r="D21">
-        <v>399.0849779563056</v>
+        <v>400.7807479283722</v>
       </c>
       <c r="E21">
-        <v>-37.81599999999999</v>
+        <v>-34.07999999999998</v>
       </c>
       <c r="F21">
-        <v>70.98400000000001</v>
+        <v>74.72000000000001</v>
       </c>
       <c r="G21">
         <v>8.08</v>
@@ -3009,28 +3009,28 @@
         <v>28.275</v>
       </c>
       <c r="M21">
-        <v>3.854431200000001</v>
+        <v>4.057296000000001</v>
       </c>
       <c r="N21">
-        <v>24.4205688</v>
+        <v>24.217704</v>
       </c>
       <c r="O21">
-        <v>7.326170639999999</v>
+        <v>7.265311199999999</v>
       </c>
       <c r="P21">
-        <v>17.09439816</v>
+        <v>16.9523928</v>
       </c>
       <c r="Q21">
-        <v>45.19439816</v>
+        <v>45.0523928</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1447725702587959</v>
+        <v>0.1456909265575917</v>
       </c>
       <c r="T21">
-        <v>0.8477776317257893</v>
+        <v>0.8556440731654508</v>
       </c>
       <c r="U21">
         <v>0.0543</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>7.335712724616799</v>
+        <v>6.968927088385958</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1241547412460734</v>
+        <v>0.1238218005825221</v>
       </c>
       <c r="C22">
-        <v>334.1407479283721</v>
+        <v>332.1149905420725</v>
       </c>
       <c r="D22">
-        <v>400.7807479283722</v>
+        <v>402.4909905420726</v>
       </c>
       <c r="E22">
-        <v>-34.07999999999998</v>
+        <v>-30.34399999999998</v>
       </c>
       <c r="F22">
-        <v>74.72000000000001</v>
+        <v>78.45600000000002</v>
       </c>
       <c r="G22">
         <v>8.08</v>
@@ -3091,28 +3091,28 @@
         <v>28.275</v>
       </c>
       <c r="M22">
-        <v>4.057296000000001</v>
+        <v>4.260160800000001</v>
       </c>
       <c r="N22">
-        <v>24.217704</v>
+        <v>24.0148392</v>
       </c>
       <c r="O22">
-        <v>7.265311199999999</v>
+        <v>7.204451759999999</v>
       </c>
       <c r="P22">
-        <v>16.9523928</v>
+        <v>16.81038744</v>
       </c>
       <c r="Q22">
-        <v>45.0523928</v>
+        <v>44.91038744</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1456909265575917</v>
+        <v>0.1466325323829394</v>
       </c>
       <c r="T22">
-        <v>0.8556440731654508</v>
+        <v>0.8637096650213061</v>
       </c>
       <c r="U22">
         <v>0.0543</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>6.968927088385958</v>
+        <v>6.637073417510435</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1238218005825221</v>
+        <v>0.1234888599189708</v>
       </c>
       <c r="C23">
-        <v>332.1149905420725</v>
+        <v>330.1038918677487</v>
       </c>
       <c r="D23">
-        <v>402.4909905420726</v>
+        <v>404.2158918677487</v>
       </c>
       <c r="E23">
-        <v>-30.34399999999999</v>
+        <v>-26.60799999999999</v>
       </c>
       <c r="F23">
-        <v>78.456</v>
+        <v>82.19200000000001</v>
       </c>
       <c r="G23">
         <v>8.08</v>
@@ -3173,28 +3173,28 @@
         <v>28.275</v>
       </c>
       <c r="M23">
-        <v>4.2601608</v>
+        <v>4.463025600000001</v>
       </c>
       <c r="N23">
-        <v>24.0148392</v>
+        <v>23.8119744</v>
       </c>
       <c r="O23">
-        <v>7.204451759999999</v>
+        <v>7.143592319999999</v>
       </c>
       <c r="P23">
-        <v>16.81038744</v>
+        <v>16.66838208</v>
       </c>
       <c r="Q23">
-        <v>44.91038744</v>
+        <v>44.76838207999999</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1466325323829394</v>
+        <v>0.1475982819473984</v>
       </c>
       <c r="T23">
-        <v>0.863709665021306</v>
+        <v>0.8719820669247473</v>
       </c>
       <c r="U23">
         <v>0.0543</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>6.637073417510437</v>
+        <v>6.335388262169053</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1234888599189708</v>
+        <v>0.1233169192554195</v>
       </c>
       <c r="C24">
-        <v>330.1038918677487</v>
+        <v>327.2644851448461</v>
       </c>
       <c r="D24">
-        <v>404.2158918677487</v>
+        <v>405.1124851448461</v>
       </c>
       <c r="E24">
-        <v>-26.60799999999999</v>
+        <v>-22.87199999999999</v>
       </c>
       <c r="F24">
-        <v>82.19200000000001</v>
+        <v>85.92800000000001</v>
       </c>
       <c r="G24">
         <v>8.08</v>
@@ -3255,45 +3255,45 @@
         <v>28.275</v>
       </c>
       <c r="M24">
-        <v>4.463025600000001</v>
+        <v>4.751818400000001</v>
       </c>
       <c r="N24">
-        <v>23.8119744</v>
+        <v>23.5231816</v>
       </c>
       <c r="O24">
-        <v>7.143592319999999</v>
+        <v>7.056954479999999</v>
       </c>
       <c r="P24">
-        <v>16.66838208</v>
+        <v>16.46622712</v>
       </c>
       <c r="Q24">
-        <v>44.76838207999999</v>
+        <v>44.56622712</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1475982819473984</v>
+        <v>0.1485891159161292</v>
       </c>
       <c r="T24">
-        <v>0.8719820669247473</v>
+        <v>0.8804693364100963</v>
       </c>
       <c r="U24">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V24">
         <v>0.3</v>
       </c>
       <c r="W24">
-        <v>0.03801</v>
+        <v>0.03871</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y24">
-        <v>6.335388262169053</v>
+        <v>5.950353658296367</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1233169192554195</v>
+        <v>0.1229909785918682</v>
       </c>
       <c r="C25">
-        <v>327.2644851448461</v>
+        <v>325.2390818315287</v>
       </c>
       <c r="D25">
-        <v>405.1124851448461</v>
+        <v>406.8230818315287</v>
       </c>
       <c r="E25">
-        <v>-22.87199999999999</v>
+        <v>-19.13599999999998</v>
       </c>
       <c r="F25">
-        <v>85.92800000000001</v>
+        <v>89.66400000000002</v>
       </c>
       <c r="G25">
         <v>8.08</v>
@@ -3337,28 +3337,28 @@
         <v>28.275</v>
       </c>
       <c r="M25">
-        <v>4.751818400000001</v>
+        <v>4.958419200000001</v>
       </c>
       <c r="N25">
-        <v>23.5231816</v>
+        <v>23.3165808</v>
       </c>
       <c r="O25">
-        <v>7.056954479999999</v>
+        <v>6.994974239999999</v>
       </c>
       <c r="P25">
-        <v>16.46622712</v>
+        <v>16.32160656</v>
       </c>
       <c r="Q25">
-        <v>44.56622712</v>
+        <v>44.42160656</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1485891159161292</v>
+        <v>0.1496060244629845</v>
       </c>
       <c r="T25">
-        <v>0.8804693364100963</v>
+        <v>0.8891799550924281</v>
       </c>
       <c r="U25">
         <v>0.0553</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>5.950353658296367</v>
+        <v>5.702422255867353</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1229909785918682</v>
+        <v>0.1226650379283169</v>
       </c>
       <c r="C26">
-        <v>325.2390818315287</v>
+        <v>323.228185842585</v>
       </c>
       <c r="D26">
-        <v>406.8230818315287</v>
+        <v>408.548185842585</v>
       </c>
       <c r="E26">
-        <v>-19.136</v>
+        <v>-15.39999999999999</v>
       </c>
       <c r="F26">
-        <v>89.664</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="G26">
         <v>8.08</v>
@@ -3419,28 +3419,28 @@
         <v>28.275</v>
       </c>
       <c r="M26">
-        <v>4.958419200000001</v>
+        <v>5.16502</v>
       </c>
       <c r="N26">
-        <v>23.3165808</v>
+        <v>23.10998</v>
       </c>
       <c r="O26">
-        <v>6.994974239999999</v>
+        <v>6.932994</v>
       </c>
       <c r="P26">
-        <v>16.32160656</v>
+        <v>16.176986</v>
       </c>
       <c r="Q26">
-        <v>44.42160656</v>
+        <v>44.276986</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1496060244629845</v>
+        <v>0.1506500505710892</v>
       </c>
       <c r="T26">
-        <v>0.8891799550924281</v>
+        <v>0.8981228569396221</v>
       </c>
       <c r="U26">
         <v>0.0553</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>5.702422255867353</v>
+        <v>5.47432536563266</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1226650379283169</v>
+        <v>0.1223390972647656</v>
       </c>
       <c r="C27">
-        <v>323.228185842585</v>
+        <v>321.2319825157229</v>
       </c>
       <c r="D27">
-        <v>408.548185842585</v>
+        <v>410.2879825157229</v>
       </c>
       <c r="E27">
-        <v>-15.39999999999999</v>
+        <v>-11.66399999999999</v>
       </c>
       <c r="F27">
-        <v>93.40000000000001</v>
+        <v>97.13600000000001</v>
       </c>
       <c r="G27">
         <v>8.08</v>
@@ -3501,28 +3501,28 @@
         <v>28.275</v>
       </c>
       <c r="M27">
-        <v>5.16502</v>
+        <v>5.371620800000001</v>
       </c>
       <c r="N27">
-        <v>23.10998</v>
+        <v>22.9033792</v>
       </c>
       <c r="O27">
-        <v>6.932994</v>
+        <v>6.871013759999999</v>
       </c>
       <c r="P27">
-        <v>16.176986</v>
+        <v>16.03236544</v>
       </c>
       <c r="Q27">
-        <v>44.276986</v>
+        <v>44.13236544</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1506500505710892</v>
+        <v>0.1517222936010346</v>
       </c>
       <c r="T27">
-        <v>0.8981228569396221</v>
+        <v>0.9073074588367401</v>
       </c>
       <c r="U27">
         <v>0.0553</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>5.47432536563266</v>
+        <v>5.263774390031402</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1223390972647656</v>
+        <v>0.1220131566012143</v>
       </c>
       <c r="C28">
-        <v>321.2319825157229</v>
+        <v>319.2506603591829</v>
       </c>
       <c r="D28">
-        <v>410.2879825157229</v>
+        <v>412.0426603591829</v>
       </c>
       <c r="E28">
-        <v>-11.66399999999999</v>
+        <v>-7.927999999999983</v>
       </c>
       <c r="F28">
-        <v>97.13600000000001</v>
+        <v>100.872</v>
       </c>
       <c r="G28">
         <v>8.08</v>
@@ -3583,28 +3583,28 @@
         <v>28.275</v>
       </c>
       <c r="M28">
-        <v>5.371620800000001</v>
+        <v>5.578221600000001</v>
       </c>
       <c r="N28">
-        <v>22.9033792</v>
+        <v>22.6967784</v>
       </c>
       <c r="O28">
-        <v>6.871013759999999</v>
+        <v>6.80903352</v>
       </c>
       <c r="P28">
-        <v>16.03236544</v>
+        <v>15.88774488</v>
       </c>
       <c r="Q28">
-        <v>44.13236544</v>
+        <v>43.98774488</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1517222936010346</v>
+        <v>0.1528239131523484</v>
       </c>
       <c r="T28">
-        <v>0.9073074588367401</v>
+        <v>0.9167436936625466</v>
       </c>
       <c r="U28">
         <v>0.0553</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>5.263774390031402</v>
+        <v>5.068819782993202</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1220131566012143</v>
+        <v>0.121687215937663</v>
       </c>
       <c r="C29">
-        <v>319.2506603591829</v>
+        <v>317.2844111198281</v>
       </c>
       <c r="D29">
-        <v>412.0426603591829</v>
+        <v>413.8124111198281</v>
       </c>
       <c r="E29">
-        <v>-7.927999999999983</v>
+        <v>-4.191999999999979</v>
       </c>
       <c r="F29">
-        <v>100.872</v>
+        <v>104.608</v>
       </c>
       <c r="G29">
         <v>8.08</v>
@@ -3665,28 +3665,28 @@
         <v>28.275</v>
       </c>
       <c r="M29">
-        <v>5.578221600000001</v>
+        <v>5.784822400000001</v>
       </c>
       <c r="N29">
-        <v>22.6967784</v>
+        <v>22.4901776</v>
       </c>
       <c r="O29">
-        <v>6.80903352</v>
+        <v>6.747053279999998</v>
       </c>
       <c r="P29">
-        <v>15.88774488</v>
+        <v>15.74312432</v>
       </c>
       <c r="Q29">
-        <v>43.98774488</v>
+        <v>43.84312432</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1528239131523484</v>
+        <v>0.1539561332467542</v>
       </c>
       <c r="T29">
-        <v>0.9167436936625466</v>
+        <v>0.9264420461224029</v>
       </c>
       <c r="U29">
         <v>0.0553</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>5.068819782993202</v>
+        <v>4.887790505029159</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.121687215937663</v>
+        <v>0.1213612752741117</v>
       </c>
       <c r="C30">
-        <v>317.2844111198281</v>
+        <v>315.3334298529934</v>
       </c>
       <c r="D30">
-        <v>413.8124111198281</v>
+        <v>415.5974298529935</v>
       </c>
       <c r="E30">
-        <v>-4.191999999999979</v>
+        <v>-0.4559999999999746</v>
       </c>
       <c r="F30">
-        <v>104.608</v>
+        <v>108.344</v>
       </c>
       <c r="G30">
         <v>8.08</v>
@@ -3747,28 +3747,28 @@
         <v>28.275</v>
       </c>
       <c r="M30">
-        <v>5.784822400000001</v>
+        <v>5.991423200000002</v>
       </c>
       <c r="N30">
-        <v>22.4901776</v>
+        <v>22.2835768</v>
       </c>
       <c r="O30">
-        <v>6.747053279999998</v>
+        <v>6.68507304</v>
       </c>
       <c r="P30">
-        <v>15.74312432</v>
+        <v>15.59850376</v>
       </c>
       <c r="Q30">
-        <v>43.84312432</v>
+        <v>43.69850376</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1539561332467542</v>
+        <v>0.1551202468649461</v>
       </c>
       <c r="T30">
-        <v>0.9264420461224029</v>
+        <v>0.9364135916092976</v>
       </c>
       <c r="U30">
         <v>0.0553</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>4.887790505029159</v>
+        <v>4.71924600485574</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1213612752741117</v>
+        <v>0.1210353346105604</v>
       </c>
       <c r="C31">
-        <v>315.3334298529934</v>
+        <v>313.3979149941533</v>
       </c>
       <c r="D31">
-        <v>415.5974298529935</v>
+        <v>417.3979149941533</v>
       </c>
       <c r="E31">
-        <v>-0.4560000000000031</v>
+        <v>3.280000000000001</v>
       </c>
       <c r="F31">
-        <v>108.344</v>
+        <v>112.08</v>
       </c>
       <c r="G31">
         <v>8.08</v>
@@ -3829,28 +3829,28 @@
         <v>28.275</v>
       </c>
       <c r="M31">
-        <v>5.9914232</v>
+        <v>6.198024</v>
       </c>
       <c r="N31">
-        <v>22.2835768</v>
+        <v>22.076976</v>
       </c>
       <c r="O31">
-        <v>6.68507304</v>
+        <v>6.623092799999999</v>
       </c>
       <c r="P31">
-        <v>15.59850376</v>
+        <v>15.4538832</v>
       </c>
       <c r="Q31">
-        <v>43.69850376</v>
+        <v>43.5538832</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1551202468649461</v>
+        <v>0.1563176208722292</v>
       </c>
       <c r="T31">
-        <v>0.9364135916092976</v>
+        <v>0.9466700383958179</v>
       </c>
       <c r="U31">
         <v>0.0553</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>4.719246004855741</v>
+        <v>4.561937804693883</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1210353346105604</v>
+        <v>0.1212518939470091</v>
       </c>
       <c r="C32">
-        <v>313.3979149941533</v>
+        <v>308.463914377102</v>
       </c>
       <c r="D32">
-        <v>417.3979149941533</v>
+        <v>416.1999143771021</v>
       </c>
       <c r="E32">
-        <v>3.280000000000001</v>
+        <v>7.016000000000005</v>
       </c>
       <c r="F32">
-        <v>112.08</v>
+        <v>115.816</v>
       </c>
       <c r="G32">
         <v>8.08</v>
@@ -3911,45 +3911,45 @@
         <v>28.275</v>
       </c>
       <c r="M32">
-        <v>6.198024</v>
+        <v>6.6941648</v>
       </c>
       <c r="N32">
-        <v>22.076976</v>
+        <v>21.5808352</v>
       </c>
       <c r="O32">
-        <v>6.623092799999999</v>
+        <v>6.47425056</v>
       </c>
       <c r="P32">
-        <v>15.4538832</v>
+        <v>15.10658464</v>
       </c>
       <c r="Q32">
-        <v>43.5538832</v>
+        <v>43.20658464</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1563176208722292</v>
+        <v>0.157549701372477</v>
       </c>
       <c r="T32">
-        <v>0.9466700383958179</v>
+        <v>0.9572237734949908</v>
       </c>
       <c r="U32">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V32">
         <v>0.3</v>
       </c>
       <c r="W32">
-        <v>0.03871</v>
+        <v>0.04046</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y32">
-        <v>4.561937804693883</v>
+        <v>4.223827892614773</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1212518939470091</v>
+        <v>0.1209434532834578</v>
       </c>
       <c r="C33">
-        <v>308.463914377102</v>
+        <v>306.4362864594471</v>
       </c>
       <c r="D33">
-        <v>416.1999143771021</v>
+        <v>417.9082864594471</v>
       </c>
       <c r="E33">
-        <v>7.016000000000005</v>
+        <v>10.75200000000001</v>
       </c>
       <c r="F33">
-        <v>115.816</v>
+        <v>119.552</v>
       </c>
       <c r="G33">
         <v>8.08</v>
@@ -3993,28 +3993,28 @@
         <v>28.275</v>
       </c>
       <c r="M33">
-        <v>6.6941648</v>
+        <v>6.910105600000001</v>
       </c>
       <c r="N33">
-        <v>21.5808352</v>
+        <v>21.3648944</v>
       </c>
       <c r="O33">
-        <v>6.47425056</v>
+        <v>6.409468319999999</v>
       </c>
       <c r="P33">
-        <v>15.10658464</v>
+        <v>14.95542608</v>
       </c>
       <c r="Q33">
-        <v>43.20658464</v>
+        <v>43.05542608</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.157549701372477</v>
+        <v>0.1588180195344968</v>
       </c>
       <c r="T33">
-        <v>0.9572237734949908</v>
+        <v>0.9680879125676689</v>
       </c>
       <c r="U33">
         <v>0.0578</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>4.223827892614773</v>
+        <v>4.091833270970562</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1209434532834578</v>
+        <v>0.1214435126199065</v>
       </c>
       <c r="C34">
-        <v>306.4362864594471</v>
+        <v>299.9376048601221</v>
       </c>
       <c r="D34">
-        <v>417.9082864594471</v>
+        <v>415.1456048601221</v>
       </c>
       <c r="E34">
-        <v>10.75200000000001</v>
+        <v>14.48800000000001</v>
       </c>
       <c r="F34">
-        <v>119.552</v>
+        <v>123.288</v>
       </c>
       <c r="G34">
         <v>8.08</v>
@@ -4075,45 +4075,45 @@
         <v>28.275</v>
       </c>
       <c r="M34">
-        <v>6.910105600000001</v>
+        <v>7.557554400000001</v>
       </c>
       <c r="N34">
-        <v>21.3648944</v>
+        <v>20.7174456</v>
       </c>
       <c r="O34">
-        <v>6.409468319999999</v>
+        <v>6.215233679999999</v>
       </c>
       <c r="P34">
-        <v>14.95542608</v>
+        <v>14.50221192</v>
       </c>
       <c r="Q34">
-        <v>43.05542608</v>
+        <v>42.60221192</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1588180195344968</v>
+        <v>0.160124197940159</v>
       </c>
       <c r="T34">
-        <v>0.9680879125676689</v>
+        <v>0.9792763542992331</v>
       </c>
       <c r="U34">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V34">
         <v>0.3</v>
       </c>
       <c r="W34">
-        <v>0.04046</v>
+        <v>0.04291</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y34">
-        <v>4.091833270970562</v>
+        <v>3.741289642585966</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1214435126199065</v>
+        <v>0.1211595719563552</v>
       </c>
       <c r="C35">
-        <v>299.9376048601221</v>
+        <v>297.7657952536485</v>
       </c>
       <c r="D35">
-        <v>415.1456048601221</v>
+        <v>416.7097952536485</v>
       </c>
       <c r="E35">
-        <v>14.48800000000001</v>
+        <v>18.22400000000002</v>
       </c>
       <c r="F35">
-        <v>123.288</v>
+        <v>127.024</v>
       </c>
       <c r="G35">
         <v>8.08</v>
@@ -4157,28 +4157,28 @@
         <v>28.275</v>
       </c>
       <c r="M35">
-        <v>7.557554400000001</v>
+        <v>7.786571200000001</v>
       </c>
       <c r="N35">
-        <v>20.7174456</v>
+        <v>20.4884288</v>
       </c>
       <c r="O35">
-        <v>6.215233679999999</v>
+        <v>6.146528639999999</v>
       </c>
       <c r="P35">
-        <v>14.50221192</v>
+        <v>14.34190016</v>
       </c>
       <c r="Q35">
-        <v>42.60221192</v>
+        <v>42.44190016</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.160124197940159</v>
+        <v>0.1614699575096291</v>
       </c>
       <c r="T35">
-        <v>0.9792763542992331</v>
+        <v>0.9908038397196322</v>
       </c>
       <c r="U35">
         <v>0.0613</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>3.741289642585966</v>
+        <v>3.631251711921673</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1211595719563552</v>
+        <v>0.1208756312928039</v>
       </c>
       <c r="C36">
-        <v>297.7657952536485</v>
+        <v>295.6058173760756</v>
       </c>
       <c r="D36">
-        <v>416.7097952536485</v>
+        <v>418.2858173760757</v>
       </c>
       <c r="E36">
-        <v>18.22400000000002</v>
+        <v>21.96000000000002</v>
       </c>
       <c r="F36">
-        <v>127.024</v>
+        <v>130.76</v>
       </c>
       <c r="G36">
         <v>8.08</v>
@@ -4239,28 +4239,28 @@
         <v>28.275</v>
       </c>
       <c r="M36">
-        <v>7.786571200000001</v>
+        <v>8.015588000000001</v>
       </c>
       <c r="N36">
-        <v>20.4884288</v>
+        <v>20.259412</v>
       </c>
       <c r="O36">
-        <v>6.146528639999999</v>
+        <v>6.077823599999999</v>
       </c>
       <c r="P36">
-        <v>14.34190016</v>
+        <v>14.1815884</v>
       </c>
       <c r="Q36">
-        <v>42.44190016</v>
+        <v>42.2815884</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1614699575096291</v>
+        <v>0.1628571250658522</v>
       </c>
       <c r="T36">
-        <v>0.9908038397196322</v>
+        <v>1.002686016999121</v>
       </c>
       <c r="U36">
         <v>0.0613</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>3.631251711921673</v>
+        <v>3.527501663009625</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1208756312928039</v>
+        <v>0.1212972906292526</v>
       </c>
       <c r="C37">
-        <v>295.6058173760756</v>
+        <v>289.5336524788898</v>
       </c>
       <c r="D37">
-        <v>418.2858173760757</v>
+        <v>415.9496524788898</v>
       </c>
       <c r="E37">
-        <v>21.96000000000002</v>
+        <v>25.69600000000004</v>
       </c>
       <c r="F37">
-        <v>130.76</v>
+        <v>134.496</v>
       </c>
       <c r="G37">
         <v>8.08</v>
@@ -4321,45 +4321,45 @@
         <v>28.275</v>
       </c>
       <c r="M37">
-        <v>8.015588000000001</v>
+        <v>8.621193600000003</v>
       </c>
       <c r="N37">
-        <v>20.259412</v>
+        <v>19.65380639999999</v>
       </c>
       <c r="O37">
-        <v>6.077823599999999</v>
+        <v>5.896141919999998</v>
       </c>
       <c r="P37">
-        <v>14.1815884</v>
+        <v>13.75766448</v>
       </c>
       <c r="Q37">
-        <v>42.2815884</v>
+        <v>41.85766448</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1628571250658522</v>
+        <v>0.1642876416082072</v>
       </c>
       <c r="T37">
-        <v>1.002686016999121</v>
+        <v>1.014939512318593</v>
       </c>
       <c r="U37">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V37">
         <v>0.3</v>
       </c>
       <c r="W37">
-        <v>0.04291</v>
+        <v>0.04487</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y37">
-        <v>3.527501663009625</v>
+        <v>3.279708276125476</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1212972906292526</v>
+        <v>0.1210329499657013</v>
       </c>
       <c r="C38">
-        <v>289.5336524788897</v>
+        <v>287.259145178436</v>
       </c>
       <c r="D38">
-        <v>415.9496524788898</v>
+        <v>417.4111451784361</v>
       </c>
       <c r="E38">
-        <v>25.69600000000001</v>
+        <v>29.432</v>
       </c>
       <c r="F38">
-        <v>134.496</v>
+        <v>138.232</v>
       </c>
       <c r="G38">
         <v>8.08</v>
@@ -4403,28 +4403,28 @@
         <v>28.275</v>
       </c>
       <c r="M38">
-        <v>8.621193600000002</v>
+        <v>8.860671200000001</v>
       </c>
       <c r="N38">
-        <v>19.6538064</v>
+        <v>19.4143288</v>
       </c>
       <c r="O38">
-        <v>5.896141919999999</v>
+        <v>5.824298639999999</v>
       </c>
       <c r="P38">
-        <v>13.75766448</v>
+        <v>13.59003016</v>
       </c>
       <c r="Q38">
-        <v>41.85766448</v>
+        <v>41.69003016000001</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1642876416082072</v>
+        <v>0.1657635713741291</v>
       </c>
       <c r="T38">
-        <v>1.014939512318593</v>
+        <v>1.027582007489477</v>
       </c>
       <c r="U38">
         <v>0.0641</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>3.279708276125477</v>
+        <v>3.19106751190587</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1210329499657013</v>
+        <v>0.12076860930215</v>
       </c>
       <c r="C39">
-        <v>287.259145178436</v>
+        <v>284.9949443770242</v>
       </c>
       <c r="D39">
-        <v>417.4111451784361</v>
+        <v>418.8829443770243</v>
       </c>
       <c r="E39">
-        <v>29.432</v>
+        <v>33.16800000000002</v>
       </c>
       <c r="F39">
-        <v>138.232</v>
+        <v>141.968</v>
       </c>
       <c r="G39">
         <v>8.08</v>
@@ -4485,28 +4485,28 @@
         <v>28.275</v>
       </c>
       <c r="M39">
-        <v>8.860671200000001</v>
+        <v>9.100148800000001</v>
       </c>
       <c r="N39">
-        <v>19.4143288</v>
+        <v>19.1748512</v>
       </c>
       <c r="O39">
-        <v>5.824298639999999</v>
+        <v>5.75245536</v>
       </c>
       <c r="P39">
-        <v>13.59003016</v>
+        <v>13.42239584</v>
       </c>
       <c r="Q39">
-        <v>41.69003016000001</v>
+        <v>41.52239584</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1657635713741291</v>
+        <v>0.1672871117776613</v>
       </c>
       <c r="T39">
-        <v>1.027582007489477</v>
+        <v>1.040632325085229</v>
       </c>
       <c r="U39">
         <v>0.0641</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>3.19106751190587</v>
+        <v>3.107092051066242</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.12076860930215</v>
+        <v>0.1205042686385987</v>
       </c>
       <c r="C40">
-        <v>284.9949443770242</v>
+        <v>282.7411594831331</v>
       </c>
       <c r="D40">
-        <v>418.8829443770243</v>
+        <v>420.3651594831331</v>
       </c>
       <c r="E40">
-        <v>33.16800000000002</v>
+        <v>36.90400000000001</v>
       </c>
       <c r="F40">
-        <v>141.968</v>
+        <v>145.704</v>
       </c>
       <c r="G40">
         <v>8.08</v>
@@ -4567,28 +4567,28 @@
         <v>28.275</v>
       </c>
       <c r="M40">
-        <v>9.100148800000001</v>
+        <v>9.339626400000002</v>
       </c>
       <c r="N40">
-        <v>19.1748512</v>
+        <v>18.9353736</v>
       </c>
       <c r="O40">
-        <v>5.75245536</v>
+        <v>5.68061208</v>
       </c>
       <c r="P40">
-        <v>13.42239584</v>
+        <v>13.25476152</v>
       </c>
       <c r="Q40">
-        <v>41.52239584</v>
+        <v>41.35476152</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1672871117776613</v>
+        <v>0.1688606043255717</v>
       </c>
       <c r="T40">
-        <v>1.040632325085229</v>
+        <v>1.054110521946415</v>
       </c>
       <c r="U40">
         <v>0.0641</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>3.107092051066242</v>
+        <v>3.027423024115825</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1205042686385987</v>
+        <v>0.1224239279750474</v>
       </c>
       <c r="C41">
-        <v>282.7411594831331</v>
+        <v>268.4737507646668</v>
       </c>
       <c r="D41">
-        <v>420.3651594831331</v>
+        <v>409.8337507646668</v>
       </c>
       <c r="E41">
-        <v>36.90400000000001</v>
+        <v>40.64000000000003</v>
       </c>
       <c r="F41">
-        <v>145.704</v>
+        <v>149.44</v>
       </c>
       <c r="G41">
         <v>8.08</v>
@@ -4649,45 +4649,45 @@
         <v>28.275</v>
       </c>
       <c r="M41">
-        <v>9.339626400000002</v>
+        <v>10.744736</v>
       </c>
       <c r="N41">
-        <v>18.9353736</v>
+        <v>17.530264</v>
       </c>
       <c r="O41">
-        <v>5.68061208</v>
+        <v>5.259079199999999</v>
       </c>
       <c r="P41">
-        <v>13.25476152</v>
+        <v>12.2711848</v>
       </c>
       <c r="Q41">
-        <v>41.35476152</v>
+        <v>40.37118479999999</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1688606043255717</v>
+        <v>0.1704865466250791</v>
       </c>
       <c r="T41">
-        <v>1.054110521946415</v>
+        <v>1.068037992036307</v>
       </c>
       <c r="U41">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V41">
         <v>0.3</v>
       </c>
       <c r="W41">
-        <v>0.04487</v>
+        <v>0.05033</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y41">
-        <v>3.027423024115825</v>
+        <v>2.631521146727104</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1224239279750474</v>
+        <v>0.1222141873114961</v>
       </c>
       <c r="C42">
-        <v>268.4737507646668</v>
+        <v>265.8626570923451</v>
       </c>
       <c r="D42">
-        <v>409.8337507646668</v>
+        <v>410.9586570923451</v>
       </c>
       <c r="E42">
-        <v>40.64000000000003</v>
+        <v>44.37600000000002</v>
       </c>
       <c r="F42">
-        <v>149.44</v>
+        <v>153.176</v>
       </c>
       <c r="G42">
         <v>8.08</v>
@@ -4731,28 +4731,28 @@
         <v>28.275</v>
       </c>
       <c r="M42">
-        <v>10.744736</v>
+        <v>11.0133544</v>
       </c>
       <c r="N42">
-        <v>17.530264</v>
+        <v>17.26164559999999</v>
       </c>
       <c r="O42">
-        <v>5.259079199999999</v>
+        <v>5.178493679999998</v>
       </c>
       <c r="P42">
-        <v>12.2711848</v>
+        <v>12.08315192</v>
       </c>
       <c r="Q42">
-        <v>40.37118479999999</v>
+        <v>40.18315192</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1704865466250791</v>
+        <v>0.1721676056127053</v>
       </c>
       <c r="T42">
-        <v>1.068037992036307</v>
+        <v>1.082437579756365</v>
       </c>
       <c r="U42">
         <v>0.07190000000000001</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>2.631521146727104</v>
+        <v>2.567337704124003</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1222141873114961</v>
+        <v>0.1220044466479449</v>
       </c>
       <c r="C43">
-        <v>265.8626570923451</v>
+        <v>263.2577556728374</v>
       </c>
       <c r="D43">
-        <v>410.9586570923451</v>
+        <v>412.0897556728374</v>
       </c>
       <c r="E43">
-        <v>44.37600000000002</v>
+        <v>48.11200000000004</v>
       </c>
       <c r="F43">
-        <v>153.176</v>
+        <v>156.912</v>
       </c>
       <c r="G43">
         <v>8.08</v>
@@ -4813,28 +4813,28 @@
         <v>28.275</v>
       </c>
       <c r="M43">
-        <v>11.0133544</v>
+        <v>11.2819728</v>
       </c>
       <c r="N43">
-        <v>17.26164559999999</v>
+        <v>16.99302719999999</v>
       </c>
       <c r="O43">
-        <v>5.178493679999998</v>
+        <v>5.097908159999998</v>
       </c>
       <c r="P43">
-        <v>12.08315192</v>
+        <v>11.89511904</v>
       </c>
       <c r="Q43">
-        <v>40.18315192</v>
+        <v>39.99511904</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1721676056127053</v>
+        <v>0.173906632151629</v>
       </c>
       <c r="T43">
-        <v>1.082437579756365</v>
+        <v>1.097333704984012</v>
       </c>
       <c r="U43">
         <v>0.07190000000000001</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>2.567337704124003</v>
+        <v>2.506210615930574</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1220044466479449</v>
+        <v>0.1229686059843935</v>
       </c>
       <c r="C44">
-        <v>263.2577556728374</v>
+        <v>254.373027374348</v>
       </c>
       <c r="D44">
-        <v>412.0897556728374</v>
+        <v>406.941027374348</v>
       </c>
       <c r="E44">
-        <v>48.11200000000001</v>
+        <v>51.848</v>
       </c>
       <c r="F44">
-        <v>156.912</v>
+        <v>160.648</v>
       </c>
       <c r="G44">
         <v>8.08</v>
@@ -4895,45 +4895,45 @@
         <v>28.275</v>
       </c>
       <c r="M44">
-        <v>11.2819728</v>
+        <v>12.1771184</v>
       </c>
       <c r="N44">
-        <v>16.9930272</v>
+        <v>16.0978816</v>
       </c>
       <c r="O44">
-        <v>5.097908159999998</v>
+        <v>4.829364479999999</v>
       </c>
       <c r="P44">
-        <v>11.89511904</v>
+        <v>11.26851712</v>
       </c>
       <c r="Q44">
-        <v>39.99511904</v>
+        <v>39.36851712</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.173906632151629</v>
+        <v>0.1757066771656027</v>
       </c>
       <c r="T44">
-        <v>1.097333704984012</v>
+        <v>1.112752501272277</v>
       </c>
       <c r="U44">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V44">
         <v>0.3</v>
       </c>
       <c r="W44">
-        <v>0.05033</v>
+        <v>0.05306</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y44">
-        <v>2.506210615930575</v>
+        <v>2.32197791556334</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1229686059843935</v>
+        <v>0.1227861653208422</v>
       </c>
       <c r="C45">
-        <v>254.373027374348</v>
+        <v>251.6013901368133</v>
       </c>
       <c r="D45">
-        <v>406.941027374348</v>
+        <v>407.9053901368134</v>
       </c>
       <c r="E45">
-        <v>51.848</v>
+        <v>55.58400000000002</v>
       </c>
       <c r="F45">
-        <v>160.648</v>
+        <v>164.384</v>
       </c>
       <c r="G45">
         <v>8.08</v>
@@ -4977,28 +4977,28 @@
         <v>28.275</v>
       </c>
       <c r="M45">
-        <v>12.1771184</v>
+        <v>12.4603072</v>
       </c>
       <c r="N45">
-        <v>16.0978816</v>
+        <v>15.8146928</v>
       </c>
       <c r="O45">
-        <v>4.829364479999999</v>
+        <v>4.744407839999998</v>
       </c>
       <c r="P45">
-        <v>11.26851712</v>
+        <v>11.07028496</v>
       </c>
       <c r="Q45">
-        <v>39.36851712</v>
+        <v>39.17028496</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1757066771656027</v>
+        <v>0.177571009501504</v>
       </c>
       <c r="T45">
-        <v>1.112752501272277</v>
+        <v>1.128721968856552</v>
       </c>
       <c r="U45">
         <v>0.07580000000000001</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>2.32197791556334</v>
+        <v>2.269205690209628</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1227861653208422</v>
+        <v>0.122603724657291</v>
       </c>
       <c r="C46">
-        <v>251.6013901368133</v>
+        <v>248.8343344214137</v>
       </c>
       <c r="D46">
-        <v>407.9053901368134</v>
+        <v>408.8743344214137</v>
       </c>
       <c r="E46">
-        <v>55.58400000000002</v>
+        <v>59.32000000000001</v>
       </c>
       <c r="F46">
-        <v>164.384</v>
+        <v>168.12</v>
       </c>
       <c r="G46">
         <v>8.08</v>
@@ -5059,28 +5059,28 @@
         <v>28.275</v>
       </c>
       <c r="M46">
-        <v>12.4603072</v>
+        <v>12.743496</v>
       </c>
       <c r="N46">
-        <v>15.8146928</v>
+        <v>15.531504</v>
       </c>
       <c r="O46">
-        <v>4.744407839999998</v>
+        <v>4.659451199999999</v>
       </c>
       <c r="P46">
-        <v>11.07028496</v>
+        <v>10.8720528</v>
       </c>
       <c r="Q46">
-        <v>39.17028496</v>
+        <v>38.9720528</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.177571009501504</v>
+        <v>0.179503135740529</v>
       </c>
       <c r="T46">
-        <v>1.128721968856552</v>
+        <v>1.145272144352983</v>
       </c>
       <c r="U46">
         <v>0.07580000000000001</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>2.269205690209628</v>
+        <v>2.218778897093858</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.122603724657291</v>
+        <v>0.1224212839937396</v>
       </c>
       <c r="C47">
-        <v>248.8343344214137</v>
+        <v>246.0718929549284</v>
       </c>
       <c r="D47">
-        <v>408.8743344214137</v>
+        <v>409.8478929549284</v>
       </c>
       <c r="E47">
-        <v>59.32000000000001</v>
+        <v>63.05600000000003</v>
       </c>
       <c r="F47">
-        <v>168.12</v>
+        <v>171.856</v>
       </c>
       <c r="G47">
         <v>8.08</v>
@@ -5141,28 +5141,28 @@
         <v>28.275</v>
       </c>
       <c r="M47">
-        <v>12.743496</v>
+        <v>13.0266848</v>
       </c>
       <c r="N47">
-        <v>15.531504</v>
+        <v>15.2483152</v>
       </c>
       <c r="O47">
-        <v>4.659451199999999</v>
+        <v>4.574494559999998</v>
       </c>
       <c r="P47">
-        <v>10.8720528</v>
+        <v>10.67382064</v>
       </c>
       <c r="Q47">
-        <v>38.9720528</v>
+        <v>38.77382064</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.179503135740529</v>
+        <v>0.1815068222106289</v>
       </c>
       <c r="T47">
-        <v>1.145272144352983</v>
+        <v>1.162435289312243</v>
       </c>
       <c r="U47">
         <v>0.07580000000000001</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>2.218778897093858</v>
+        <v>2.170544573243991</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1224212839937396</v>
+        <v>0.1222388433301884</v>
       </c>
       <c r="C48">
-        <v>246.0718929549284</v>
+        <v>243.3140987765785</v>
       </c>
       <c r="D48">
-        <v>409.8478929549284</v>
+        <v>410.8260987765785</v>
       </c>
       <c r="E48">
-        <v>63.05600000000003</v>
+        <v>66.79200000000002</v>
       </c>
       <c r="F48">
-        <v>171.856</v>
+        <v>175.592</v>
       </c>
       <c r="G48">
         <v>8.08</v>
@@ -5223,28 +5223,28 @@
         <v>28.275</v>
       </c>
       <c r="M48">
-        <v>13.0266848</v>
+        <v>13.3098736</v>
       </c>
       <c r="N48">
-        <v>15.2483152</v>
+        <v>14.9651264</v>
       </c>
       <c r="O48">
-        <v>4.574494559999998</v>
+        <v>4.489537919999999</v>
       </c>
       <c r="P48">
-        <v>10.67382064</v>
+        <v>10.47558848</v>
       </c>
       <c r="Q48">
-        <v>38.77382064</v>
+        <v>38.57558848</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1815068222106289</v>
+        <v>0.1835861194909214</v>
       </c>
       <c r="T48">
-        <v>1.162435289312243</v>
+        <v>1.180246100119024</v>
       </c>
       <c r="U48">
         <v>0.07580000000000001</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>2.170544573243991</v>
+        <v>2.124362773813269</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1222388433301884</v>
+        <v>0.1220564026666371</v>
       </c>
       <c r="C49">
-        <v>243.3140987765785</v>
+        <v>240.5609852417668</v>
       </c>
       <c r="D49">
-        <v>410.8260987765785</v>
+        <v>411.8089852417668</v>
       </c>
       <c r="E49">
-        <v>66.79200000000002</v>
+        <v>70.52800000000003</v>
       </c>
       <c r="F49">
-        <v>175.592</v>
+        <v>179.328</v>
       </c>
       <c r="G49">
         <v>8.08</v>
@@ -5305,28 +5305,28 @@
         <v>28.275</v>
       </c>
       <c r="M49">
-        <v>13.3098736</v>
+        <v>13.5930624</v>
       </c>
       <c r="N49">
-        <v>14.9651264</v>
+        <v>14.6819376</v>
       </c>
       <c r="O49">
-        <v>4.489537919999999</v>
+        <v>4.404581279999999</v>
       </c>
       <c r="P49">
-        <v>10.47558848</v>
+        <v>10.27735632</v>
       </c>
       <c r="Q49">
-        <v>38.57558848</v>
+        <v>38.37735632</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1835861194909214</v>
+        <v>0.1857453897435328</v>
       </c>
       <c r="T49">
-        <v>1.180246100119024</v>
+        <v>1.198741942110681</v>
       </c>
       <c r="U49">
         <v>0.07580000000000001</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>2.124362773813269</v>
+        <v>2.080105216025492</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1220564026666371</v>
+        <v>0.1218739620030857</v>
       </c>
       <c r="C50">
-        <v>240.5609852417668</v>
+        <v>237.8125860258676</v>
       </c>
       <c r="D50">
-        <v>411.8089852417668</v>
+        <v>412.7965860258676</v>
       </c>
       <c r="E50">
-        <v>70.52800000000001</v>
+        <v>74.26400000000002</v>
       </c>
       <c r="F50">
-        <v>179.328</v>
+        <v>183.064</v>
       </c>
       <c r="G50">
         <v>8.08</v>
@@ -5387,28 +5387,28 @@
         <v>28.275</v>
       </c>
       <c r="M50">
-        <v>13.5930624</v>
+        <v>13.8762512</v>
       </c>
       <c r="N50">
-        <v>14.6819376</v>
+        <v>14.3987488</v>
       </c>
       <c r="O50">
-        <v>4.404581279999999</v>
+        <v>4.319624639999999</v>
       </c>
       <c r="P50">
-        <v>10.27735632</v>
+        <v>10.07912416</v>
       </c>
       <c r="Q50">
-        <v>38.37735632</v>
+        <v>38.17912416</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1857453897435328</v>
+        <v>0.1879893372609524</v>
       </c>
       <c r="T50">
-        <v>1.198741942110681</v>
+        <v>1.217963111239265</v>
       </c>
       <c r="U50">
         <v>0.07580000000000001</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>2.080105216025492</v>
+        <v>2.037654089167829</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1218739620030857</v>
+        <v>0.1266615213395345</v>
       </c>
       <c r="C51">
-        <v>237.8125860258676</v>
+        <v>209.6361832639168</v>
       </c>
       <c r="D51">
-        <v>412.7965860258676</v>
+        <v>388.3561832639169</v>
       </c>
       <c r="E51">
-        <v>74.26400000000002</v>
+        <v>78.00000000000001</v>
       </c>
       <c r="F51">
-        <v>183.064</v>
+        <v>186.8</v>
       </c>
       <c r="G51">
         <v>8.08</v>
@@ -5469,45 +5469,45 @@
         <v>28.275</v>
       </c>
       <c r="M51">
-        <v>13.8762512</v>
+        <v>16.812</v>
       </c>
       <c r="N51">
-        <v>14.3987488</v>
+        <v>11.463</v>
       </c>
       <c r="O51">
-        <v>4.319624639999999</v>
+        <v>3.438899999999999</v>
       </c>
       <c r="P51">
-        <v>10.07912416</v>
+        <v>8.024099999999999</v>
       </c>
       <c r="Q51">
-        <v>38.17912416</v>
+        <v>36.1241</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1879893372609524</v>
+        <v>0.1903230426790689</v>
       </c>
       <c r="T51">
-        <v>1.217963111239265</v>
+        <v>1.237953127132992</v>
       </c>
       <c r="U51">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V51">
         <v>0.3</v>
       </c>
       <c r="W51">
-        <v>0.05306</v>
+        <v>0.063</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y51">
-        <v>2.037654089167829</v>
+        <v>1.681834403997145</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1266615213395345</v>
+        <v>0.1265784806759832</v>
       </c>
       <c r="C52">
-        <v>209.6361832639168</v>
+        <v>206.2994152732666</v>
       </c>
       <c r="D52">
-        <v>388.3561832639169</v>
+        <v>388.7554152732666</v>
       </c>
       <c r="E52">
-        <v>78.00000000000001</v>
+        <v>81.736</v>
       </c>
       <c r="F52">
-        <v>186.8</v>
+        <v>190.536</v>
       </c>
       <c r="G52">
         <v>8.08</v>
@@ -5551,28 +5551,28 @@
         <v>28.275</v>
       </c>
       <c r="M52">
-        <v>16.812</v>
+        <v>17.14824</v>
       </c>
       <c r="N52">
-        <v>11.463</v>
+        <v>11.12676</v>
       </c>
       <c r="O52">
-        <v>3.438899999999999</v>
+        <v>3.338027999999999</v>
       </c>
       <c r="P52">
-        <v>8.024099999999999</v>
+        <v>7.788731999999998</v>
       </c>
       <c r="Q52">
-        <v>36.1241</v>
+        <v>35.888732</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1903230426790689</v>
+        <v>0.1927520013795575</v>
       </c>
       <c r="T52">
-        <v>1.237953127132992</v>
+        <v>1.258759062042791</v>
       </c>
       <c r="U52">
         <v>0.09</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>1.681834403997145</v>
+        <v>1.64885725882073</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1265784806759832</v>
+        <v>0.1264954400124318</v>
       </c>
       <c r="C53">
-        <v>206.2994152732666</v>
+        <v>202.9634689521173</v>
       </c>
       <c r="D53">
-        <v>388.7554152732666</v>
+        <v>389.1554689521174</v>
       </c>
       <c r="E53">
-        <v>81.736</v>
+        <v>85.47200000000002</v>
       </c>
       <c r="F53">
-        <v>190.536</v>
+        <v>194.272</v>
       </c>
       <c r="G53">
         <v>8.08</v>
@@ -5633,28 +5633,28 @@
         <v>28.275</v>
       </c>
       <c r="M53">
-        <v>17.14824</v>
+        <v>17.48448</v>
       </c>
       <c r="N53">
-        <v>11.12676</v>
+        <v>10.79052</v>
       </c>
       <c r="O53">
-        <v>3.338027999999999</v>
+        <v>3.237155999999999</v>
       </c>
       <c r="P53">
-        <v>7.788731999999998</v>
+        <v>7.553363999999998</v>
       </c>
       <c r="Q53">
-        <v>35.888732</v>
+        <v>35.653364</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1927520013795575</v>
+        <v>0.1952821666925663</v>
       </c>
       <c r="T53">
-        <v>1.258759062042791</v>
+        <v>1.280431910907164</v>
       </c>
       <c r="U53">
         <v>0.09</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>1.64885725882073</v>
+        <v>1.61714846538187</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1264954400124318</v>
+        <v>0.1264123993488805</v>
       </c>
       <c r="C54">
-        <v>202.9634689521173</v>
+        <v>199.6283468397304</v>
       </c>
       <c r="D54">
-        <v>389.1554689521174</v>
+        <v>389.5563468397305</v>
       </c>
       <c r="E54">
-        <v>85.47200000000002</v>
+        <v>89.20800000000001</v>
       </c>
       <c r="F54">
-        <v>194.272</v>
+        <v>198.008</v>
       </c>
       <c r="G54">
         <v>8.08</v>
@@ -5715,28 +5715,28 @@
         <v>28.275</v>
       </c>
       <c r="M54">
-        <v>17.48448</v>
+        <v>17.82072</v>
       </c>
       <c r="N54">
-        <v>10.79052</v>
+        <v>10.45428</v>
       </c>
       <c r="O54">
-        <v>3.237155999999999</v>
+        <v>3.136283999999999</v>
       </c>
       <c r="P54">
-        <v>7.553363999999998</v>
+        <v>7.317995999999998</v>
       </c>
       <c r="Q54">
-        <v>35.653364</v>
+        <v>35.417996</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1952821666925663</v>
+        <v>0.1979199986146395</v>
       </c>
       <c r="T54">
-        <v>1.280431910907164</v>
+        <v>1.303027008659383</v>
       </c>
       <c r="U54">
         <v>0.09</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>1.61714846538187</v>
+        <v>1.586636230185986</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1264123993488805</v>
+        <v>0.1263293586853292</v>
       </c>
       <c r="C55">
-        <v>199.6283468397304</v>
+        <v>196.2940514858409</v>
       </c>
       <c r="D55">
-        <v>389.5563468397305</v>
+        <v>389.9580514858409</v>
       </c>
       <c r="E55">
-        <v>89.20800000000001</v>
+        <v>92.94400000000003</v>
       </c>
       <c r="F55">
-        <v>198.008</v>
+        <v>201.744</v>
       </c>
       <c r="G55">
         <v>8.08</v>
@@ -5797,28 +5797,28 @@
         <v>28.275</v>
       </c>
       <c r="M55">
-        <v>17.82072</v>
+        <v>18.15696</v>
       </c>
       <c r="N55">
-        <v>10.45428</v>
+        <v>10.11804</v>
       </c>
       <c r="O55">
-        <v>3.136283999999999</v>
+        <v>3.035411999999999</v>
       </c>
       <c r="P55">
-        <v>7.317995999999998</v>
+        <v>7.082627999999998</v>
       </c>
       <c r="Q55">
-        <v>35.417996</v>
+        <v>35.182628</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1979199986146395</v>
+        <v>0.2006725188811506</v>
       </c>
       <c r="T55">
-        <v>1.303027008659383</v>
+        <v>1.326604501966046</v>
       </c>
       <c r="U55">
         <v>0.09</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>1.586636230185986</v>
+        <v>1.557254077775134</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1263293586853292</v>
+        <v>0.126246318021778</v>
       </c>
       <c r="C56">
-        <v>196.2940514858409</v>
+        <v>192.9605854507114</v>
       </c>
       <c r="D56">
-        <v>389.9580514858409</v>
+        <v>390.3605854507115</v>
       </c>
       <c r="E56">
-        <v>92.94400000000003</v>
+        <v>96.68000000000002</v>
       </c>
       <c r="F56">
-        <v>201.744</v>
+        <v>205.48</v>
       </c>
       <c r="G56">
         <v>8.08</v>
@@ -5879,28 +5879,28 @@
         <v>28.275</v>
       </c>
       <c r="M56">
-        <v>18.15696</v>
+        <v>18.4932</v>
       </c>
       <c r="N56">
-        <v>10.11804</v>
+        <v>9.781799999999997</v>
       </c>
       <c r="O56">
-        <v>3.035411999999999</v>
+        <v>2.934539999999999</v>
       </c>
       <c r="P56">
-        <v>7.082627999999998</v>
+        <v>6.847259999999999</v>
       </c>
       <c r="Q56">
-        <v>35.182628</v>
+        <v>34.94726</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.2006725188811506</v>
+        <v>0.2035473733817288</v>
       </c>
       <c r="T56">
-        <v>1.326604501966046</v>
+        <v>1.351229883864116</v>
       </c>
       <c r="U56">
         <v>0.09</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>1.557254077775134</v>
+        <v>1.528940367270132</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.126246318021778</v>
+        <v>0.1261632773582267</v>
       </c>
       <c r="C57">
-        <v>192.9605854507114</v>
+        <v>189.6279513051876</v>
       </c>
       <c r="D57">
-        <v>390.3605854507115</v>
+        <v>390.7639513051877</v>
       </c>
       <c r="E57">
-        <v>96.68000000000002</v>
+        <v>100.416</v>
       </c>
       <c r="F57">
-        <v>205.48</v>
+        <v>209.216</v>
       </c>
       <c r="G57">
         <v>8.08</v>
@@ -5961,28 +5961,28 @@
         <v>28.275</v>
       </c>
       <c r="M57">
-        <v>18.4932</v>
+        <v>18.82944</v>
       </c>
       <c r="N57">
-        <v>9.781799999999997</v>
+        <v>9.445559999999997</v>
       </c>
       <c r="O57">
-        <v>2.934539999999999</v>
+        <v>2.833667999999999</v>
       </c>
       <c r="P57">
-        <v>6.847259999999999</v>
+        <v>6.611891999999997</v>
       </c>
       <c r="Q57">
-        <v>34.94726</v>
+        <v>34.711892</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.2035473733817288</v>
+        <v>0.2065529030868788</v>
       </c>
       <c r="T57">
-        <v>1.351229883864116</v>
+        <v>1.376974601303008</v>
       </c>
       <c r="U57">
         <v>0.09</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>1.528940367270132</v>
+        <v>1.501637860711736</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1261632773582267</v>
+        <v>0.1525302019793181</v>
       </c>
       <c r="C58">
-        <v>189.6279513051876</v>
+        <v>89.35654279260686</v>
       </c>
       <c r="D58">
-        <v>390.7639513051877</v>
+        <v>294.2285427926069</v>
       </c>
       <c r="E58">
-        <v>100.416</v>
+        <v>104.152</v>
       </c>
       <c r="F58">
-        <v>209.216</v>
+        <v>212.952</v>
       </c>
       <c r="G58">
         <v>8.08</v>
@@ -6043,45 +6043,45 @@
         <v>28.275</v>
       </c>
       <c r="M58">
-        <v>18.82944</v>
+        <v>31.26135360000001</v>
       </c>
       <c r="N58">
-        <v>9.445559999999997</v>
+        <v>-2.986353600000008</v>
       </c>
       <c r="O58">
-        <v>2.833667999999999</v>
+        <v>-0.8959060800000024</v>
       </c>
       <c r="P58">
-        <v>6.611891999999997</v>
+        <v>-2.090447520000006</v>
       </c>
       <c r="Q58">
-        <v>34.711892</v>
+        <v>26.00955248</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.2065529030868788</v>
+        <v>0.2129278289146035</v>
       </c>
       <c r="T58">
-        <v>1.376974601303008</v>
+        <v>1.43158083721791</v>
       </c>
       <c r="U58">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V58">
-        <v>0.3</v>
+        <v>0.2713414175386186</v>
       </c>
       <c r="W58">
-        <v>0.063</v>
+        <v>0.1069670799053308</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y58">
-        <v>1.501637860711736</v>
+        <v>0.9044713917953954</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1525302019793181</v>
+        <v>0.1535402019793181</v>
       </c>
       <c r="C59">
-        <v>89.35654279260686</v>
+        <v>82.86232605678174</v>
       </c>
       <c r="D59">
-        <v>294.2285427926069</v>
+        <v>291.4703260567818</v>
       </c>
       <c r="E59">
-        <v>104.152</v>
+        <v>107.888</v>
       </c>
       <c r="F59">
-        <v>212.952</v>
+        <v>216.688</v>
       </c>
       <c r="G59">
         <v>8.08</v>
@@ -6125,37 +6125,37 @@
         <v>28.275</v>
       </c>
       <c r="M59">
-        <v>31.26135360000001</v>
+        <v>31.80979840000001</v>
       </c>
       <c r="N59">
-        <v>-2.986353600000008</v>
+        <v>-3.53479840000001</v>
       </c>
       <c r="O59">
-        <v>-0.8959060800000024</v>
+        <v>-1.060439520000003</v>
       </c>
       <c r="P59">
-        <v>-2.090447520000006</v>
+        <v>-2.474358880000008</v>
       </c>
       <c r="Q59">
-        <v>26.00955248</v>
+        <v>25.62564111999999</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.2129278289146035</v>
+        <v>0.2169070629363798</v>
       </c>
       <c r="T59">
-        <v>1.43158083721791</v>
+        <v>1.465666095246908</v>
       </c>
       <c r="U59">
         <v>0.1468</v>
       </c>
       <c r="V59">
-        <v>0.2713414175386186</v>
+        <v>0.2666631172362286</v>
       </c>
       <c r="W59">
-        <v>0.1069670799053308</v>
+        <v>0.1076538543897217</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.9044713917953954</v>
+        <v>0.8888770574540954</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1535402019793181</v>
+        <v>0.1545502019793181</v>
       </c>
       <c r="C60">
-        <v>82.8623260567818</v>
+        <v>76.41934230907961</v>
       </c>
       <c r="D60">
-        <v>291.4703260567818</v>
+        <v>288.7633423090796</v>
       </c>
       <c r="E60">
-        <v>107.888</v>
+        <v>111.624</v>
       </c>
       <c r="F60">
-        <v>216.688</v>
+        <v>220.424</v>
       </c>
       <c r="G60">
         <v>8.08</v>
@@ -6207,37 +6207,37 @@
         <v>28.275</v>
       </c>
       <c r="M60">
-        <v>31.8097984</v>
+        <v>32.3582432</v>
       </c>
       <c r="N60">
-        <v>-3.534798400000003</v>
+        <v>-4.083243200000005</v>
       </c>
       <c r="O60">
-        <v>-1.060439520000001</v>
+        <v>-1.224972960000002</v>
       </c>
       <c r="P60">
-        <v>-2.474358880000002</v>
+        <v>-2.858270240000004</v>
       </c>
       <c r="Q60">
-        <v>25.62564112</v>
+        <v>25.24172976</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.2169070629363798</v>
+        <v>0.2210804059348281</v>
       </c>
       <c r="T60">
-        <v>1.465666095246908</v>
+        <v>1.501414048789515</v>
       </c>
       <c r="U60">
         <v>0.1468</v>
       </c>
       <c r="V60">
-        <v>0.2666631172362287</v>
+        <v>0.2621434033847672</v>
       </c>
       <c r="W60">
-        <v>0.1076538543897217</v>
+        <v>0.1083173483831162</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.8888770574540956</v>
+        <v>0.8738113446158905</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1545502019793181</v>
+        <v>0.1555602019793181</v>
       </c>
       <c r="C61">
-        <v>76.41934230907961</v>
+        <v>70.02617723036437</v>
       </c>
       <c r="D61">
-        <v>288.7633423090796</v>
+        <v>286.1061772303644</v>
       </c>
       <c r="E61">
-        <v>111.624</v>
+        <v>115.36</v>
       </c>
       <c r="F61">
-        <v>220.424</v>
+        <v>224.16</v>
       </c>
       <c r="G61">
         <v>8.08</v>
@@ -6289,37 +6289,37 @@
         <v>28.275</v>
       </c>
       <c r="M61">
-        <v>32.3582432</v>
+        <v>32.906688</v>
       </c>
       <c r="N61">
-        <v>-4.083243200000005</v>
+        <v>-4.631688000000004</v>
       </c>
       <c r="O61">
-        <v>-1.224972960000002</v>
+        <v>-1.389506400000001</v>
       </c>
       <c r="P61">
-        <v>-2.858270240000004</v>
+        <v>-3.242181600000003</v>
       </c>
       <c r="Q61">
-        <v>25.24172976</v>
+        <v>24.8578184</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.2210804059348281</v>
+        <v>0.2254624160831988</v>
       </c>
       <c r="T61">
-        <v>1.501414048789515</v>
+        <v>1.538949400009253</v>
       </c>
       <c r="U61">
         <v>0.1468</v>
       </c>
       <c r="V61">
-        <v>0.2621434033847672</v>
+        <v>0.2577743466616877</v>
       </c>
       <c r="W61">
-        <v>0.1083173483831162</v>
+        <v>0.1089587259100643</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.8738113446158905</v>
+        <v>0.8592478222056257</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1555602019793181</v>
+        <v>0.1565702019793181</v>
       </c>
       <c r="C62">
-        <v>70.02617723036437</v>
+        <v>63.68146808440986</v>
       </c>
       <c r="D62">
-        <v>286.1061772303644</v>
+        <v>283.4974680844099</v>
       </c>
       <c r="E62">
-        <v>115.36</v>
+        <v>119.096</v>
       </c>
       <c r="F62">
-        <v>224.16</v>
+        <v>227.896</v>
       </c>
       <c r="G62">
         <v>8.08</v>
@@ -6371,37 +6371,37 @@
         <v>28.275</v>
       </c>
       <c r="M62">
-        <v>32.906688</v>
+        <v>33.45513280000001</v>
       </c>
       <c r="N62">
-        <v>-4.631688000000004</v>
+        <v>-5.18013280000001</v>
       </c>
       <c r="O62">
-        <v>-1.389506400000001</v>
+        <v>-1.554039840000003</v>
       </c>
       <c r="P62">
-        <v>-3.242181600000003</v>
+        <v>-3.626092960000007</v>
       </c>
       <c r="Q62">
-        <v>24.8578184</v>
+        <v>24.47390703999999</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.2254624160831988</v>
+        <v>0.2300691447007167</v>
       </c>
       <c r="T62">
-        <v>1.538949400009253</v>
+        <v>1.578409641035132</v>
       </c>
       <c r="U62">
         <v>0.1468</v>
       </c>
       <c r="V62">
-        <v>0.2577743466616877</v>
+        <v>0.2535485377000206</v>
       </c>
       <c r="W62">
-        <v>0.1089587259100643</v>
+        <v>0.109579074665637</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.8592478222056257</v>
+        <v>0.8451617923334022</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1565702019793181</v>
+        <v>0.157580201979318</v>
       </c>
       <c r="C63">
-        <v>63.68146808440986</v>
+        <v>57.38390138748963</v>
       </c>
       <c r="D63">
-        <v>283.4974680844099</v>
+        <v>280.9359013874897</v>
       </c>
       <c r="E63">
-        <v>119.096</v>
+        <v>122.832</v>
       </c>
       <c r="F63">
-        <v>227.896</v>
+        <v>231.632</v>
       </c>
       <c r="G63">
         <v>8.08</v>
@@ -6453,37 +6453,37 @@
         <v>28.275</v>
       </c>
       <c r="M63">
-        <v>33.45513280000001</v>
+        <v>34.00357760000001</v>
       </c>
       <c r="N63">
-        <v>-5.18013280000001</v>
+        <v>-5.728577600000008</v>
       </c>
       <c r="O63">
-        <v>-1.554039840000003</v>
+        <v>-1.718573280000002</v>
       </c>
       <c r="P63">
-        <v>-3.626092960000007</v>
+        <v>-4.010004320000006</v>
       </c>
       <c r="Q63">
-        <v>24.47390703999999</v>
+        <v>24.08999567999999</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.2300691447007167</v>
+        <v>0.2349183327191566</v>
       </c>
       <c r="T63">
-        <v>1.578409641035132</v>
+        <v>1.619946736851845</v>
       </c>
       <c r="U63">
         <v>0.1468</v>
       </c>
       <c r="V63">
-        <v>0.2535485377000206</v>
+        <v>0.2494590451564719</v>
       </c>
       <c r="W63">
-        <v>0.109579074665637</v>
+        <v>0.1101794121710299</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.8451617923334022</v>
+        <v>0.8315301505215731</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.157580201979318</v>
+        <v>0.1585902019793181</v>
       </c>
       <c r="C64">
-        <v>57.38390138748963</v>
+        <v>51.13221070317471</v>
       </c>
       <c r="D64">
-        <v>280.9359013874897</v>
+        <v>278.4202107031747</v>
       </c>
       <c r="E64">
-        <v>122.832</v>
+        <v>126.568</v>
       </c>
       <c r="F64">
-        <v>231.632</v>
+        <v>235.368</v>
       </c>
       <c r="G64">
         <v>8.08</v>
@@ -6535,37 +6535,37 @@
         <v>28.275</v>
       </c>
       <c r="M64">
-        <v>34.00357760000001</v>
+        <v>34.55202240000001</v>
       </c>
       <c r="N64">
-        <v>-5.728577600000008</v>
+        <v>-6.277022400000007</v>
       </c>
       <c r="O64">
-        <v>-1.718573280000002</v>
+        <v>-1.883106720000002</v>
       </c>
       <c r="P64">
-        <v>-4.010004320000006</v>
+        <v>-4.393915680000005</v>
       </c>
       <c r="Q64">
-        <v>24.08999567999999</v>
+        <v>23.70608432</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.2349183327191566</v>
+        <v>0.2400296390088636</v>
       </c>
       <c r="T64">
-        <v>1.619946736851845</v>
+        <v>1.663729081091085</v>
       </c>
       <c r="U64">
         <v>0.1468</v>
       </c>
       <c r="V64">
-        <v>0.2494590451564719</v>
+        <v>0.2454993777730359</v>
       </c>
       <c r="W64">
-        <v>0.1101794121710299</v>
+        <v>0.1107606913429183</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.8315301505215731</v>
+        <v>0.818331259243453</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1585902019793181</v>
+        <v>0.1596002019793181</v>
       </c>
       <c r="C65">
-        <v>51.13221070317471</v>
+        <v>44.92517455456297</v>
       </c>
       <c r="D65">
-        <v>278.4202107031747</v>
+        <v>275.949174554563</v>
       </c>
       <c r="E65">
-        <v>126.568</v>
+        <v>130.304</v>
       </c>
       <c r="F65">
-        <v>235.368</v>
+        <v>239.104</v>
       </c>
       <c r="G65">
         <v>8.08</v>
@@ -6617,37 +6617,37 @@
         <v>28.275</v>
       </c>
       <c r="M65">
-        <v>34.55202240000001</v>
+        <v>35.1004672</v>
       </c>
       <c r="N65">
-        <v>-6.277022400000007</v>
+        <v>-6.825467200000006</v>
       </c>
       <c r="O65">
-        <v>-1.883106720000002</v>
+        <v>-2.047640160000002</v>
       </c>
       <c r="P65">
-        <v>-4.393915680000005</v>
+        <v>-4.777827040000004</v>
       </c>
       <c r="Q65">
-        <v>23.70608432</v>
+        <v>23.32217296</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2400296390088636</v>
+        <v>0.2454249067591098</v>
       </c>
       <c r="T65">
-        <v>1.663729081091085</v>
+        <v>1.70994377778806</v>
       </c>
       <c r="U65">
         <v>0.1468</v>
       </c>
       <c r="V65">
-        <v>0.2454993777730359</v>
+        <v>0.2416634499953322</v>
       </c>
       <c r="W65">
-        <v>0.1107606913429183</v>
+        <v>0.1113238055406852</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.818331259243453</v>
+        <v>0.805544833317774</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1596002019793181</v>
+        <v>0.199246176862417</v>
       </c>
       <c r="C66">
-        <v>44.92517455456297</v>
+        <v>-30.10796863337953</v>
       </c>
       <c r="D66">
-        <v>275.949174554563</v>
+        <v>204.6520313666205</v>
       </c>
       <c r="E66">
-        <v>130.304</v>
+        <v>134.04</v>
       </c>
       <c r="F66">
-        <v>239.104</v>
+        <v>242.84</v>
       </c>
       <c r="G66">
         <v>8.08</v>
@@ -6699,45 +6699,45 @@
         <v>28.275</v>
       </c>
       <c r="M66">
-        <v>35.1004672</v>
+        <v>48.76227200000001</v>
       </c>
       <c r="N66">
-        <v>-6.825467200000006</v>
+        <v>-20.48727200000001</v>
       </c>
       <c r="O66">
-        <v>-2.047640160000002</v>
+        <v>-6.146181600000003</v>
       </c>
       <c r="P66">
-        <v>-4.777827040000004</v>
+        <v>-14.34109040000001</v>
       </c>
       <c r="Q66">
-        <v>23.32217296</v>
+        <v>13.75890959999999</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2454249067591098</v>
+        <v>0.2612312609039385</v>
       </c>
       <c r="T66">
-        <v>1.70994377778806</v>
+        <v>1.845337588902418</v>
       </c>
       <c r="U66">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V66">
-        <v>0.2416634499953322</v>
+        <v>0.1739562094235477</v>
       </c>
       <c r="W66">
-        <v>0.1113238055406852</v>
+        <v>0.1658695931477516</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y66">
-        <v>0.805544833317774</v>
+        <v>0.5798540314118258</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.199246176862417</v>
+        <v>0.200796176862417</v>
       </c>
       <c r="C67">
-        <v>-30.10796863337953</v>
+        <v>-35.89053942654067</v>
       </c>
       <c r="D67">
-        <v>204.6520313666205</v>
+        <v>202.6054605734593</v>
       </c>
       <c r="E67">
-        <v>134.04</v>
+        <v>137.776</v>
       </c>
       <c r="F67">
-        <v>242.84</v>
+        <v>246.576</v>
       </c>
       <c r="G67">
         <v>8.08</v>
@@ -6781,37 +6781,37 @@
         <v>28.275</v>
       </c>
       <c r="M67">
-        <v>48.76227200000001</v>
+        <v>49.51246080000001</v>
       </c>
       <c r="N67">
-        <v>-20.48727200000001</v>
+        <v>-21.23746080000001</v>
       </c>
       <c r="O67">
-        <v>-6.146181600000003</v>
+        <v>-6.371238240000002</v>
       </c>
       <c r="P67">
-        <v>-14.34109040000001</v>
+        <v>-14.86622256000001</v>
       </c>
       <c r="Q67">
-        <v>13.75890959999999</v>
+        <v>13.23377744</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2612312609039385</v>
+        <v>0.2675674744599367</v>
       </c>
       <c r="T67">
-        <v>1.845337588902418</v>
+        <v>1.899612223870137</v>
       </c>
       <c r="U67">
         <v>0.2008</v>
       </c>
       <c r="V67">
-        <v>0.1739562094235477</v>
+        <v>0.1713205092807667</v>
       </c>
       <c r="W67">
-        <v>0.1658695931477516</v>
+        <v>0.1663988417364221</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.5798540314118258</v>
+        <v>0.5710683642692225</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.200796176862417</v>
+        <v>0.202346176862417</v>
       </c>
       <c r="C68">
-        <v>-35.89053942654067</v>
+        <v>-41.63258307566059</v>
       </c>
       <c r="D68">
-        <v>202.6054605734593</v>
+        <v>200.5994169243394</v>
       </c>
       <c r="E68">
-        <v>137.776</v>
+        <v>141.5120000000001</v>
       </c>
       <c r="F68">
-        <v>246.576</v>
+        <v>250.312</v>
       </c>
       <c r="G68">
         <v>8.08</v>
@@ -6863,37 +6863,37 @@
         <v>28.275</v>
       </c>
       <c r="M68">
-        <v>49.51246080000001</v>
+        <v>50.26264960000001</v>
       </c>
       <c r="N68">
-        <v>-21.23746080000001</v>
+        <v>-21.98764960000001</v>
       </c>
       <c r="O68">
-        <v>-6.371238240000002</v>
+        <v>-6.596294880000003</v>
       </c>
       <c r="P68">
-        <v>-14.86622256000001</v>
+        <v>-15.39135472000001</v>
       </c>
       <c r="Q68">
-        <v>13.23377744</v>
+        <v>12.70864527999999</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2675674744599367</v>
+        <v>0.2742877009587227</v>
       </c>
       <c r="T68">
-        <v>1.899612223870137</v>
+        <v>1.95717623065408</v>
       </c>
       <c r="U68">
         <v>0.2008</v>
       </c>
       <c r="V68">
-        <v>0.1713205092807667</v>
+        <v>0.1687634867541881</v>
       </c>
       <c r="W68">
-        <v>0.1663988417364221</v>
+        <v>0.166912291859759</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.5710683642692225</v>
+        <v>0.5625449558472937</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.202346176862417</v>
+        <v>0.203896176862417</v>
       </c>
       <c r="C69">
-        <v>-41.63258307566059</v>
+        <v>-47.33529158438893</v>
       </c>
       <c r="D69">
-        <v>200.5994169243394</v>
+        <v>198.6327084156111</v>
       </c>
       <c r="E69">
-        <v>141.5120000000001</v>
+        <v>145.248</v>
       </c>
       <c r="F69">
-        <v>250.312</v>
+        <v>254.048</v>
       </c>
       <c r="G69">
         <v>8.08</v>
@@ -6945,37 +6945,37 @@
         <v>28.275</v>
       </c>
       <c r="M69">
-        <v>50.26264960000001</v>
+        <v>51.01283840000001</v>
       </c>
       <c r="N69">
-        <v>-21.98764960000001</v>
+        <v>-22.73783840000001</v>
       </c>
       <c r="O69">
-        <v>-6.596294880000003</v>
+        <v>-6.821351520000002</v>
       </c>
       <c r="P69">
-        <v>-15.39135472000001</v>
+        <v>-15.91648688000001</v>
       </c>
       <c r="Q69">
-        <v>12.70864527999999</v>
+        <v>12.18351312</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2742877009587227</v>
+        <v>0.2814279416136828</v>
       </c>
       <c r="T69">
-        <v>1.95717623065408</v>
+        <v>2.01833798786202</v>
       </c>
       <c r="U69">
         <v>0.2008</v>
       </c>
       <c r="V69">
-        <v>0.1687634867541881</v>
+        <v>0.1662816707725089</v>
       </c>
       <c r="W69">
-        <v>0.166912291859759</v>
+        <v>0.1674106405088802</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.5625449558472937</v>
+        <v>0.5542722359083629</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.203896176862417</v>
+        <v>0.205446176862417</v>
       </c>
       <c r="C70">
-        <v>-47.33529158438893</v>
+        <v>-52.99981066386255</v>
       </c>
       <c r="D70">
-        <v>198.6327084156111</v>
+        <v>196.7041893361375</v>
       </c>
       <c r="E70">
-        <v>145.248</v>
+        <v>148.984</v>
       </c>
       <c r="F70">
-        <v>254.048</v>
+        <v>257.784</v>
       </c>
       <c r="G70">
         <v>8.08</v>
@@ -7027,37 +7027,37 @@
         <v>28.275</v>
       </c>
       <c r="M70">
-        <v>51.01283840000001</v>
+        <v>51.76302720000001</v>
       </c>
       <c r="N70">
-        <v>-22.73783840000001</v>
+        <v>-23.48802720000001</v>
       </c>
       <c r="O70">
-        <v>-6.821351520000002</v>
+        <v>-7.046408160000003</v>
       </c>
       <c r="P70">
-        <v>-15.91648688000001</v>
+        <v>-16.44161904000001</v>
       </c>
       <c r="Q70">
-        <v>12.18351312</v>
+        <v>11.65838095999999</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2814279416136828</v>
+        <v>0.2890288429560596</v>
       </c>
       <c r="T70">
-        <v>2.01833798786202</v>
+        <v>2.083445664889827</v>
       </c>
       <c r="U70">
         <v>0.2008</v>
       </c>
       <c r="V70">
-        <v>0.1662816707725089</v>
+        <v>0.1638717914859507</v>
       </c>
       <c r="W70">
-        <v>0.1674106405088802</v>
+        <v>0.1678945442696211</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.5542722359083629</v>
+        <v>0.5462393049531692</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.205446176862417</v>
+        <v>0.2069961768624171</v>
       </c>
       <c r="C71">
-        <v>-52.99981066386255</v>
+        <v>-58.6272419583606</v>
       </c>
       <c r="D71">
-        <v>196.7041893361375</v>
+        <v>194.8127580416394</v>
       </c>
       <c r="E71">
-        <v>148.984</v>
+        <v>152.72</v>
       </c>
       <c r="F71">
-        <v>257.784</v>
+        <v>261.52</v>
       </c>
       <c r="G71">
         <v>8.08</v>
@@ -7109,37 +7109,37 @@
         <v>28.275</v>
       </c>
       <c r="M71">
-        <v>51.76302720000001</v>
+        <v>52.51321600000001</v>
       </c>
       <c r="N71">
-        <v>-23.48802720000001</v>
+        <v>-24.23821600000001</v>
       </c>
       <c r="O71">
-        <v>-7.046408160000003</v>
+        <v>-7.271464800000002</v>
       </c>
       <c r="P71">
-        <v>-16.44161904000001</v>
+        <v>-16.9667512</v>
       </c>
       <c r="Q71">
-        <v>11.65838095999999</v>
+        <v>11.1332488</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2890288429560596</v>
+        <v>0.297136471054595</v>
       </c>
       <c r="T71">
-        <v>2.083445664889827</v>
+        <v>2.152893853719488</v>
       </c>
       <c r="U71">
         <v>0.2008</v>
       </c>
       <c r="V71">
-        <v>0.1638717914859507</v>
+        <v>0.1615307658932943</v>
       </c>
       <c r="W71">
-        <v>0.1678945442696211</v>
+        <v>0.1683646222086265</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.5462393049531692</v>
+        <v>0.538435886310981</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2069961768624171</v>
+        <v>0.2085461768624171</v>
       </c>
       <c r="C72">
-        <v>-58.6272419583606</v>
+        <v>-64.21864514377501</v>
       </c>
       <c r="D72">
-        <v>194.8127580416394</v>
+        <v>192.957354856225</v>
       </c>
       <c r="E72">
-        <v>152.72</v>
+        <v>156.456</v>
       </c>
       <c r="F72">
-        <v>261.52</v>
+        <v>265.256</v>
       </c>
       <c r="G72">
         <v>8.08</v>
@@ -7191,37 +7191,37 @@
         <v>28.275</v>
       </c>
       <c r="M72">
-        <v>52.51321600000001</v>
+        <v>53.26340480000001</v>
       </c>
       <c r="N72">
-        <v>-24.23821600000001</v>
+        <v>-24.98840480000001</v>
       </c>
       <c r="O72">
-        <v>-7.271464800000002</v>
+        <v>-7.496521440000003</v>
       </c>
       <c r="P72">
-        <v>-16.9667512</v>
+        <v>-17.49188336000001</v>
       </c>
       <c r="Q72">
-        <v>11.1332488</v>
+        <v>10.60811663999999</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.297136471054595</v>
+        <v>0.3058032459185466</v>
       </c>
       <c r="T72">
-        <v>2.152893853719488</v>
+        <v>2.227131572813264</v>
       </c>
       <c r="U72">
         <v>0.2008</v>
       </c>
       <c r="V72">
-        <v>0.1615307658932943</v>
+        <v>0.1592556846835296</v>
       </c>
       <c r="W72">
-        <v>0.1683646222086265</v>
+        <v>0.1688214585155473</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.538435886310981</v>
+        <v>0.5308522822784321</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2085461768624171</v>
+        <v>0.2100961768624171</v>
       </c>
       <c r="C73">
-        <v>-64.21864514377501</v>
+        <v>-69.7750399072977</v>
       </c>
       <c r="D73">
-        <v>192.957354856225</v>
+        <v>191.1369600927023</v>
       </c>
       <c r="E73">
-        <v>156.456</v>
+        <v>160.192</v>
       </c>
       <c r="F73">
-        <v>265.256</v>
+        <v>268.992</v>
       </c>
       <c r="G73">
         <v>8.08</v>
@@ -7273,37 +7273,37 @@
         <v>28.275</v>
       </c>
       <c r="M73">
-        <v>53.26340480000001</v>
+        <v>54.01359360000001</v>
       </c>
       <c r="N73">
-        <v>-24.98840480000001</v>
+        <v>-25.73859360000001</v>
       </c>
       <c r="O73">
-        <v>-7.496521440000003</v>
+        <v>-7.721578080000002</v>
       </c>
       <c r="P73">
-        <v>-17.49188336000001</v>
+        <v>-18.01701552000001</v>
       </c>
       <c r="Q73">
-        <v>10.60811663999999</v>
+        <v>10.08298447999999</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.3058032459185465</v>
+        <v>0.3150890761299231</v>
       </c>
       <c r="T73">
-        <v>2.227131572813263</v>
+        <v>2.306671986128022</v>
       </c>
       <c r="U73">
         <v>0.2008</v>
       </c>
       <c r="V73">
-        <v>0.1592556846835296</v>
+        <v>0.1570438001740362</v>
       </c>
       <c r="W73">
-        <v>0.1688214585155473</v>
+        <v>0.1692656049250535</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.5308522822784321</v>
+        <v>0.5234793339134538</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2100961768624171</v>
+        <v>0.211646176862417</v>
       </c>
       <c r="C74">
-        <v>-69.7750399072977</v>
+        <v>-75.29740781609468</v>
       </c>
       <c r="D74">
-        <v>191.1369600927023</v>
+        <v>189.3505921839053</v>
       </c>
       <c r="E74">
-        <v>160.192</v>
+        <v>163.928</v>
       </c>
       <c r="F74">
-        <v>268.992</v>
+        <v>272.728</v>
       </c>
       <c r="G74">
         <v>8.08</v>
@@ -7355,37 +7355,37 @@
         <v>28.275</v>
       </c>
       <c r="M74">
-        <v>54.01359360000001</v>
+        <v>54.7637824</v>
       </c>
       <c r="N74">
-        <v>-25.73859360000001</v>
+        <v>-26.48878240000001</v>
       </c>
       <c r="O74">
-        <v>-7.721578080000002</v>
+        <v>-7.946634720000001</v>
       </c>
       <c r="P74">
-        <v>-18.01701552000001</v>
+        <v>-18.54214768</v>
       </c>
       <c r="Q74">
-        <v>10.08298447999999</v>
+        <v>9.557852319999999</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.3150890761299231</v>
+        <v>0.3250627456162166</v>
       </c>
       <c r="T74">
-        <v>2.306671986128022</v>
+        <v>2.392104281910542</v>
       </c>
       <c r="U74">
         <v>0.2008</v>
       </c>
       <c r="V74">
-        <v>0.1570438001740362</v>
+        <v>0.1548925152401452</v>
       </c>
       <c r="W74">
-        <v>0.1692656049250535</v>
+        <v>0.1696975829397789</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.5234793339134538</v>
+        <v>0.5163083841338175</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.211646176862417</v>
+        <v>0.213196176862417</v>
       </c>
       <c r="C75">
-        <v>-75.29740781609468</v>
+        <v>-80.78669408216197</v>
       </c>
       <c r="D75">
-        <v>189.3505921839053</v>
+        <v>187.597305917838</v>
       </c>
       <c r="E75">
-        <v>163.928</v>
+        <v>167.664</v>
       </c>
       <c r="F75">
-        <v>272.728</v>
+        <v>276.464</v>
       </c>
       <c r="G75">
         <v>8.08</v>
@@ -7437,37 +7437,37 @@
         <v>28.275</v>
       </c>
       <c r="M75">
-        <v>54.7637824</v>
+        <v>55.5139712</v>
       </c>
       <c r="N75">
-        <v>-26.48878240000001</v>
+        <v>-27.2389712</v>
       </c>
       <c r="O75">
-        <v>-7.946634720000001</v>
+        <v>-8.171691360000001</v>
       </c>
       <c r="P75">
-        <v>-18.54214768</v>
+        <v>-19.06727984</v>
       </c>
       <c r="Q75">
-        <v>9.557852319999999</v>
+        <v>9.03272016</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.3250627456162166</v>
+        <v>0.3358036204476095</v>
       </c>
       <c r="T75">
-        <v>2.392104281910542</v>
+        <v>2.484108292753255</v>
       </c>
       <c r="U75">
         <v>0.2008</v>
       </c>
       <c r="V75">
-        <v>0.1548925152401452</v>
+        <v>0.1527993731423055</v>
       </c>
       <c r="W75">
-        <v>0.1696975829397789</v>
+        <v>0.1701178858730251</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.5163083841338175</v>
+        <v>0.5093312438076849</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.213196176862417</v>
+        <v>0.214746176862417</v>
       </c>
       <c r="C76">
-        <v>-80.78669408216197</v>
+        <v>-86.24380923003213</v>
       </c>
       <c r="D76">
-        <v>187.597305917838</v>
+        <v>185.8761907699679</v>
       </c>
       <c r="E76">
-        <v>167.664</v>
+        <v>171.4</v>
       </c>
       <c r="F76">
-        <v>276.464</v>
+        <v>280.2</v>
       </c>
       <c r="G76">
         <v>8.08</v>
@@ -7519,37 +7519,37 @@
         <v>28.275</v>
       </c>
       <c r="M76">
-        <v>55.5139712</v>
+        <v>56.26416000000001</v>
       </c>
       <c r="N76">
-        <v>-27.2389712</v>
+        <v>-27.98916000000001</v>
       </c>
       <c r="O76">
-        <v>-8.171691360000001</v>
+        <v>-8.396748000000004</v>
       </c>
       <c r="P76">
-        <v>-19.06727984</v>
+        <v>-19.59241200000001</v>
       </c>
       <c r="Q76">
-        <v>9.03272016</v>
+        <v>8.507587999999991</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.3358036204476095</v>
+        <v>0.3474037652655139</v>
       </c>
       <c r="T76">
-        <v>2.484108292753255</v>
+        <v>2.583472624463385</v>
       </c>
       <c r="U76">
         <v>0.2008</v>
       </c>
       <c r="V76">
-        <v>0.1527993731423055</v>
+        <v>0.1507620481670747</v>
       </c>
       <c r="W76">
-        <v>0.1701178858730251</v>
+        <v>0.1705269807280514</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.5093312438076849</v>
+        <v>0.5025401605569157</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.214746176862417</v>
+        <v>0.2443229854375876</v>
       </c>
       <c r="C77">
-        <v>-86.24380923003213</v>
+        <v>-117.6724439189941</v>
       </c>
       <c r="D77">
-        <v>185.8761907699679</v>
+        <v>158.1835560810059</v>
       </c>
       <c r="E77">
-        <v>171.4</v>
+        <v>175.136</v>
       </c>
       <c r="F77">
-        <v>280.2</v>
+        <v>283.936</v>
       </c>
       <c r="G77">
         <v>8.08</v>
@@ -7601,45 +7601,45 @@
         <v>28.275</v>
       </c>
       <c r="M77">
-        <v>56.26416000000001</v>
+        <v>66.9521088</v>
       </c>
       <c r="N77">
-        <v>-27.98916000000001</v>
+        <v>-38.67710880000001</v>
       </c>
       <c r="O77">
-        <v>-8.396748000000004</v>
+        <v>-11.60313264</v>
       </c>
       <c r="P77">
-        <v>-19.59241200000001</v>
+        <v>-27.07397616</v>
       </c>
       <c r="Q77">
-        <v>8.507587999999991</v>
+        <v>1.026023839999997</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.3474037652655139</v>
+        <v>0.3659156245481212</v>
       </c>
       <c r="T77">
-        <v>2.583472624463385</v>
+        <v>2.742041207459795</v>
       </c>
       <c r="U77">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.1507620481670747</v>
+        <v>0.1266950384690497</v>
       </c>
       <c r="W77">
-        <v>0.1705269807280514</v>
+        <v>0.2059253099289981</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y77">
-        <v>0.5025401605569157</v>
+        <v>0.4223167948968323</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2443229854375876</v>
+        <v>0.2462229854375876</v>
       </c>
       <c r="C78">
-        <v>-117.6724439189941</v>
+        <v>-122.9080162155434</v>
       </c>
       <c r="D78">
-        <v>158.1835560810059</v>
+        <v>156.6839837844566</v>
       </c>
       <c r="E78">
-        <v>175.136</v>
+        <v>178.872</v>
       </c>
       <c r="F78">
-        <v>283.936</v>
+        <v>287.672</v>
       </c>
       <c r="G78">
         <v>8.08</v>
@@ -7683,37 +7683,37 @@
         <v>28.275</v>
       </c>
       <c r="M78">
-        <v>66.9521088</v>
+        <v>67.8330576</v>
       </c>
       <c r="N78">
-        <v>-38.67710880000001</v>
+        <v>-39.55805760000001</v>
       </c>
       <c r="O78">
-        <v>-11.60313264</v>
+        <v>-11.86741728</v>
       </c>
       <c r="P78">
-        <v>-27.07397616</v>
+        <v>-27.69064032</v>
       </c>
       <c r="Q78">
-        <v>1.026023839999997</v>
+        <v>0.4093596799999979</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.3659156245481212</v>
+        <v>0.3798336951806482</v>
       </c>
       <c r="T78">
-        <v>2.742041207459795</v>
+        <v>2.86126039039283</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.1266950384690497</v>
+        <v>0.125049648359062</v>
       </c>
       <c r="W78">
-        <v>0.2059253099289981</v>
+        <v>0.2063132929169332</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.4223167948968323</v>
+        <v>0.4168321611968734</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2462229854375876</v>
+        <v>0.2481229854375877</v>
       </c>
       <c r="C79">
-        <v>-122.9080162155434</v>
+        <v>-128.1154237698882</v>
       </c>
       <c r="D79">
-        <v>156.6839837844566</v>
+        <v>155.2125762301118</v>
       </c>
       <c r="E79">
-        <v>178.872</v>
+        <v>182.608</v>
       </c>
       <c r="F79">
-        <v>287.672</v>
+        <v>291.408</v>
       </c>
       <c r="G79">
         <v>8.08</v>
@@ -7765,37 +7765,37 @@
         <v>28.275</v>
       </c>
       <c r="M79">
-        <v>67.8330576</v>
+        <v>68.7140064</v>
       </c>
       <c r="N79">
-        <v>-39.55805760000001</v>
+        <v>-40.4390064</v>
       </c>
       <c r="O79">
-        <v>-11.86741728</v>
+        <v>-12.13170192</v>
       </c>
       <c r="P79">
-        <v>-27.69064032</v>
+        <v>-28.30730448</v>
       </c>
       <c r="Q79">
-        <v>0.4093596799999979</v>
+        <v>-0.2073044800000012</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.3798336951806482</v>
+        <v>0.3950170449615869</v>
       </c>
       <c r="T79">
-        <v>2.86126039039283</v>
+        <v>2.991317680865232</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.125049648359062</v>
+        <v>0.123446447739074</v>
       </c>
       <c r="W79">
-        <v>0.2063132929169332</v>
+        <v>0.2066913276231264</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.4168321611968734</v>
+        <v>0.4114881591302468</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2481229854375877</v>
+        <v>0.2500229854375877</v>
       </c>
       <c r="C80">
-        <v>-128.1154237698882</v>
+        <v>-133.2954526788052</v>
       </c>
       <c r="D80">
-        <v>155.2125762301118</v>
+        <v>153.7685473211948</v>
       </c>
       <c r="E80">
-        <v>182.608</v>
+        <v>186.344</v>
       </c>
       <c r="F80">
-        <v>291.408</v>
+        <v>295.144</v>
       </c>
       <c r="G80">
         <v>8.08</v>
@@ -7847,37 +7847,37 @@
         <v>28.275</v>
       </c>
       <c r="M80">
-        <v>68.7140064</v>
+        <v>69.5949552</v>
       </c>
       <c r="N80">
-        <v>-40.4390064</v>
+        <v>-41.3199552</v>
       </c>
       <c r="O80">
-        <v>-12.13170192</v>
+        <v>-12.39598656</v>
       </c>
       <c r="P80">
-        <v>-28.30730448</v>
+        <v>-28.92396864</v>
       </c>
       <c r="Q80">
-        <v>-0.2073044800000012</v>
+        <v>-0.8239686400000004</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.3950170449615869</v>
+        <v>0.4116464280549957</v>
       </c>
       <c r="T80">
-        <v>2.991317680865232</v>
+        <v>3.133761379954052</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.123446447739074</v>
+        <v>0.1218838344765541</v>
       </c>
       <c r="W80">
-        <v>0.2066913276231264</v>
+        <v>0.2070597918304286</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.4114881591302468</v>
+        <v>0.4062794482551804</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2500229854375877</v>
+        <v>0.2519229854375877</v>
       </c>
       <c r="C81">
-        <v>-133.2954526788052</v>
+        <v>-138.4488600547465</v>
       </c>
       <c r="D81">
-        <v>153.7685473211948</v>
+        <v>152.3511399452535</v>
       </c>
       <c r="E81">
-        <v>186.344</v>
+        <v>190.08</v>
       </c>
       <c r="F81">
-        <v>295.144</v>
+        <v>298.8800000000001</v>
       </c>
       <c r="G81">
         <v>8.08</v>
@@ -7929,37 +7929,37 @@
         <v>28.275</v>
       </c>
       <c r="M81">
-        <v>69.5949552</v>
+        <v>70.47590400000001</v>
       </c>
       <c r="N81">
-        <v>-41.3199552</v>
+        <v>-42.20090400000002</v>
       </c>
       <c r="O81">
-        <v>-12.39598656</v>
+        <v>-12.6602712</v>
       </c>
       <c r="P81">
-        <v>-28.92396864</v>
+        <v>-29.54063280000001</v>
       </c>
       <c r="Q81">
-        <v>-0.8239686400000004</v>
+        <v>-1.44063280000001</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.4116464280549957</v>
+        <v>0.4299387494577456</v>
       </c>
       <c r="T81">
-        <v>3.133761379954052</v>
+        <v>3.290449448951756</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.1218838344765541</v>
+        <v>0.1203602865455972</v>
       </c>
       <c r="W81">
-        <v>0.2070597918304286</v>
+        <v>0.2074190444325482</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.4062794482551804</v>
+        <v>0.4012009551519906</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2519229854375877</v>
+        <v>0.2538229854375876</v>
       </c>
       <c r="C82">
-        <v>-138.4488600547465</v>
+        <v>-143.5763753494966</v>
       </c>
       <c r="D82">
-        <v>152.3511399452535</v>
+        <v>150.9596246505034</v>
       </c>
       <c r="E82">
-        <v>190.08</v>
+        <v>193.816</v>
       </c>
       <c r="F82">
-        <v>298.8800000000001</v>
+        <v>302.616</v>
       </c>
       <c r="G82">
         <v>8.08</v>
@@ -8011,37 +8011,37 @@
         <v>28.275</v>
       </c>
       <c r="M82">
-        <v>70.47590400000001</v>
+        <v>71.35685280000001</v>
       </c>
       <c r="N82">
-        <v>-42.20090400000002</v>
+        <v>-43.08185280000001</v>
       </c>
       <c r="O82">
-        <v>-12.6602712</v>
+        <v>-12.92455584</v>
       </c>
       <c r="P82">
-        <v>-29.54063280000001</v>
+        <v>-30.15729696000001</v>
       </c>
       <c r="Q82">
-        <v>-1.44063280000001</v>
+        <v>-2.057296960000009</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.4299387494577456</v>
+        <v>0.4501565783765742</v>
       </c>
       <c r="T82">
-        <v>3.290449448951756</v>
+        <v>3.463630998896584</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.1203602865455972</v>
+        <v>0.1188743570820713</v>
       </c>
       <c r="W82">
-        <v>0.2074190444325482</v>
+        <v>0.2077694266000476</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.4012009551519906</v>
+        <v>0.3962478569402376</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2538229854375876</v>
+        <v>0.2557229854375876</v>
       </c>
       <c r="C83">
-        <v>-143.5763753494966</v>
+        <v>-148.6787016059476</v>
       </c>
       <c r="D83">
-        <v>150.9596246505034</v>
+        <v>149.5932983940524</v>
       </c>
       <c r="E83">
-        <v>193.816</v>
+        <v>197.552</v>
       </c>
       <c r="F83">
-        <v>302.616</v>
+        <v>306.352</v>
       </c>
       <c r="G83">
         <v>8.08</v>
@@ -8093,37 +8093,37 @@
         <v>28.275</v>
       </c>
       <c r="M83">
-        <v>71.35685280000001</v>
+        <v>72.23780160000001</v>
       </c>
       <c r="N83">
-        <v>-43.08185280000001</v>
+        <v>-43.96280160000001</v>
       </c>
       <c r="O83">
-        <v>-12.92455584</v>
+        <v>-13.18884048</v>
       </c>
       <c r="P83">
-        <v>-30.15729696000001</v>
+        <v>-30.77396112000001</v>
       </c>
       <c r="Q83">
-        <v>-2.057296960000009</v>
+        <v>-2.673961120000008</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.4501565783765742</v>
+        <v>0.4726208327308284</v>
       </c>
       <c r="T83">
-        <v>3.463630998896584</v>
+        <v>3.656054943279728</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.1188743570820713</v>
+        <v>0.1174246698005826</v>
       </c>
       <c r="W83">
-        <v>0.2077694266000476</v>
+        <v>0.2081112628610226</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.3962478569402376</v>
+        <v>0.3914155660019421</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2557229854375876</v>
+        <v>0.2576229854375877</v>
       </c>
       <c r="C84">
-        <v>-148.6787016059476</v>
+        <v>-153.7565166425053</v>
       </c>
       <c r="D84">
-        <v>149.5932983940524</v>
+        <v>148.2514833574947</v>
       </c>
       <c r="E84">
-        <v>197.552</v>
+        <v>201.288</v>
       </c>
       <c r="F84">
-        <v>306.352</v>
+        <v>310.088</v>
       </c>
       <c r="G84">
         <v>8.08</v>
@@ -8175,37 +8175,37 @@
         <v>28.275</v>
       </c>
       <c r="M84">
-        <v>72.23780160000001</v>
+        <v>73.11875040000001</v>
       </c>
       <c r="N84">
-        <v>-43.96280160000001</v>
+        <v>-44.84375040000001</v>
       </c>
       <c r="O84">
-        <v>-13.18884048</v>
+        <v>-13.45312512</v>
       </c>
       <c r="P84">
-        <v>-30.77396112000001</v>
+        <v>-31.39062528000001</v>
       </c>
       <c r="Q84">
-        <v>-2.673961120000008</v>
+        <v>-3.290625280000008</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.4726208327308284</v>
+        <v>0.4977279405385243</v>
       </c>
       <c r="T84">
-        <v>3.656054943279728</v>
+        <v>3.871116998766772</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.1174246698005826</v>
+        <v>0.1160099147427443</v>
       </c>
       <c r="W84">
-        <v>0.2081112628610226</v>
+        <v>0.2084448621036609</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.3914155660019421</v>
+        <v>0.3866997158091475</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2576229854375877</v>
+        <v>0.2595229854375877</v>
       </c>
       <c r="C85">
-        <v>-153.7565166425053</v>
+        <v>-158.8104741743194</v>
       </c>
       <c r="D85">
-        <v>148.2514833574947</v>
+        <v>146.9335258256807</v>
       </c>
       <c r="E85">
-        <v>201.288</v>
+        <v>205.0240000000001</v>
       </c>
       <c r="F85">
-        <v>310.088</v>
+        <v>313.8240000000001</v>
       </c>
       <c r="G85">
         <v>8.08</v>
@@ -8257,37 +8257,37 @@
         <v>28.275</v>
       </c>
       <c r="M85">
-        <v>73.11875040000001</v>
+        <v>73.99969920000002</v>
       </c>
       <c r="N85">
-        <v>-44.84375040000001</v>
+        <v>-45.72469920000002</v>
       </c>
       <c r="O85">
-        <v>-13.45312512</v>
+        <v>-13.71740976000001</v>
       </c>
       <c r="P85">
-        <v>-31.39062528000001</v>
+        <v>-32.00728944000002</v>
       </c>
       <c r="Q85">
-        <v>-3.290625280000008</v>
+        <v>-3.907289440000014</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.4977279405385243</v>
+        <v>0.5259734368221821</v>
       </c>
       <c r="T85">
-        <v>3.871116998766772</v>
+        <v>4.113061811189696</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.1160099147427443</v>
+        <v>0.1146288443291402</v>
       </c>
       <c r="W85">
-        <v>0.2084448621036609</v>
+        <v>0.2087705185071888</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.3866997158091475</v>
+        <v>0.3820961477638005</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2595229854375877</v>
+        <v>0.2614229854375876</v>
       </c>
       <c r="C86">
-        <v>-158.8104741743193</v>
+        <v>-163.8412048752334</v>
       </c>
       <c r="D86">
-        <v>146.9335258256807</v>
+        <v>145.6387951247666</v>
       </c>
       <c r="E86">
-        <v>205.024</v>
+        <v>208.76</v>
       </c>
       <c r="F86">
-        <v>313.824</v>
+        <v>317.56</v>
       </c>
       <c r="G86">
         <v>8.08</v>
@@ -8339,37 +8339,37 @@
         <v>28.275</v>
       </c>
       <c r="M86">
-        <v>73.99969920000001</v>
+        <v>74.88064800000001</v>
       </c>
       <c r="N86">
-        <v>-45.72469920000001</v>
+        <v>-46.60564800000001</v>
       </c>
       <c r="O86">
-        <v>-13.71740976</v>
+        <v>-13.9816944</v>
       </c>
       <c r="P86">
-        <v>-32.00728944000001</v>
+        <v>-32.62395360000001</v>
       </c>
       <c r="Q86">
-        <v>-3.907289440000007</v>
+        <v>-4.523953600000006</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.5259734368221817</v>
+        <v>0.5579849992769939</v>
       </c>
       <c r="T86">
-        <v>4.113061811189692</v>
+        <v>4.387265931935672</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.1146288443291402</v>
+        <v>0.1132802696899738</v>
       </c>
       <c r="W86">
-        <v>0.2087705185071888</v>
+        <v>0.2090885124071042</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3820961477638005</v>
+        <v>0.3776008989665794</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2614229854375876</v>
+        <v>0.2633229854375876</v>
       </c>
       <c r="C87">
-        <v>-163.8412048752334</v>
+        <v>-168.8493173840811</v>
       </c>
       <c r="D87">
-        <v>145.6387951247666</v>
+        <v>144.3666826159189</v>
       </c>
       <c r="E87">
-        <v>208.76</v>
+        <v>212.496</v>
       </c>
       <c r="F87">
-        <v>317.56</v>
+        <v>321.296</v>
       </c>
       <c r="G87">
         <v>8.08</v>
@@ -8421,37 +8421,37 @@
         <v>28.275</v>
       </c>
       <c r="M87">
-        <v>74.88064800000001</v>
+        <v>75.76159680000001</v>
       </c>
       <c r="N87">
-        <v>-46.60564800000001</v>
+        <v>-47.48659680000001</v>
       </c>
       <c r="O87">
-        <v>-13.9816944</v>
+        <v>-14.24597904</v>
       </c>
       <c r="P87">
-        <v>-32.62395360000001</v>
+        <v>-33.24061776000001</v>
       </c>
       <c r="Q87">
-        <v>-4.523953600000006</v>
+        <v>-5.140617760000005</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.5579849992769939</v>
+        <v>0.5945696420824935</v>
       </c>
       <c r="T87">
-        <v>4.387265931935672</v>
+        <v>4.700642069931078</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.1132802696899738</v>
+        <v>0.1119630572517183</v>
       </c>
       <c r="W87">
-        <v>0.2090885124071042</v>
+        <v>0.2093991111000448</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3776008989665794</v>
+        <v>0.373210190839061</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2633229854375876</v>
+        <v>0.2652229854375877</v>
       </c>
       <c r="C88">
-        <v>-168.8493173840811</v>
+        <v>-173.8353992586998</v>
       </c>
       <c r="D88">
-        <v>144.3666826159189</v>
+        <v>143.1166007413002</v>
       </c>
       <c r="E88">
-        <v>212.496</v>
+        <v>216.232</v>
       </c>
       <c r="F88">
-        <v>321.296</v>
+        <v>325.032</v>
       </c>
       <c r="G88">
         <v>8.08</v>
@@ -8503,37 +8503,37 @@
         <v>28.275</v>
       </c>
       <c r="M88">
-        <v>75.76159680000001</v>
+        <v>76.64254560000001</v>
       </c>
       <c r="N88">
-        <v>-47.48659680000001</v>
+        <v>-48.36754560000001</v>
       </c>
       <c r="O88">
-        <v>-14.24597904</v>
+        <v>-14.51026368</v>
       </c>
       <c r="P88">
-        <v>-33.24061776000001</v>
+        <v>-33.85728192000001</v>
       </c>
       <c r="Q88">
-        <v>-5.140617760000005</v>
+        <v>-5.757281920000004</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.5945696420824935</v>
+        <v>0.6367826914734545</v>
       </c>
       <c r="T88">
-        <v>4.700642069931078</v>
+        <v>5.062229921464237</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.1119630572517183</v>
+        <v>0.1106761255591698</v>
       </c>
       <c r="W88">
-        <v>0.2093991111000448</v>
+        <v>0.2097025695931478</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.373210190839061</v>
+        <v>0.3689204185305661</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2652229854375877</v>
+        <v>0.2671229854375876</v>
       </c>
       <c r="C89">
-        <v>-173.8353992586998</v>
+        <v>-178.8000178808046</v>
       </c>
       <c r="D89">
-        <v>143.1166007413002</v>
+        <v>141.8879821191954</v>
       </c>
       <c r="E89">
-        <v>216.232</v>
+        <v>219.968</v>
       </c>
       <c r="F89">
-        <v>325.032</v>
+        <v>328.768</v>
       </c>
       <c r="G89">
         <v>8.08</v>
@@ -8585,37 +8585,37 @@
         <v>28.275</v>
       </c>
       <c r="M89">
-        <v>76.64254560000001</v>
+        <v>77.5234944</v>
       </c>
       <c r="N89">
-        <v>-48.36754560000001</v>
+        <v>-49.24849440000001</v>
       </c>
       <c r="O89">
-        <v>-14.51026368</v>
+        <v>-14.77454832</v>
       </c>
       <c r="P89">
-        <v>-33.85728192000001</v>
+        <v>-34.47394608</v>
       </c>
       <c r="Q89">
-        <v>-5.757281920000004</v>
+        <v>-6.373946080000003</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.6367826914734545</v>
+        <v>0.6860312490962424</v>
       </c>
       <c r="T89">
-        <v>5.062229921464237</v>
+        <v>5.484082414919591</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.1106761255591698</v>
+        <v>0.1094184423141793</v>
       </c>
       <c r="W89">
-        <v>0.2097025695931478</v>
+        <v>0.2099991313023165</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3689204185305661</v>
+        <v>0.3647281410472643</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2671229854375876</v>
+        <v>0.2690229854375876</v>
       </c>
       <c r="C90">
-        <v>-178.8000178808046</v>
+        <v>-183.7437213146513</v>
       </c>
       <c r="D90">
-        <v>141.8879821191954</v>
+        <v>140.6802786853487</v>
       </c>
       <c r="E90">
-        <v>219.968</v>
+        <v>223.704</v>
       </c>
       <c r="F90">
-        <v>328.768</v>
+        <v>332.504</v>
       </c>
       <c r="G90">
         <v>8.08</v>
@@ -8667,37 +8667,37 @@
         <v>28.275</v>
       </c>
       <c r="M90">
-        <v>77.5234944</v>
+        <v>78.4044432</v>
       </c>
       <c r="N90">
-        <v>-49.24849440000001</v>
+        <v>-50.1294432</v>
       </c>
       <c r="O90">
-        <v>-14.77454832</v>
+        <v>-15.03883296</v>
       </c>
       <c r="P90">
-        <v>-34.47394608</v>
+        <v>-35.09061024</v>
       </c>
       <c r="Q90">
-        <v>-6.373946080000003</v>
+        <v>-6.990610240000002</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.6860312490962424</v>
+        <v>0.7442340899231735</v>
       </c>
       <c r="T90">
-        <v>5.484082414919591</v>
+        <v>5.982635361730463</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.1094184423141793</v>
+        <v>0.1081890216140199</v>
       </c>
       <c r="W90">
-        <v>0.2099991313023165</v>
+        <v>0.2102890287034141</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3647281410472643</v>
+        <v>0.3606300720467331</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2690229854375876</v>
+        <v>0.2709229854375876</v>
       </c>
       <c r="C91">
-        <v>-183.7437213146513</v>
+        <v>-188.6670391222159</v>
       </c>
       <c r="D91">
-        <v>140.6802786853487</v>
+        <v>139.4929608777841</v>
       </c>
       <c r="E91">
-        <v>223.704</v>
+        <v>227.44</v>
       </c>
       <c r="F91">
-        <v>332.504</v>
+        <v>336.24</v>
       </c>
       <c r="G91">
         <v>8.08</v>
@@ -8749,37 +8749,37 @@
         <v>28.275</v>
       </c>
       <c r="M91">
-        <v>78.4044432</v>
+        <v>79.285392</v>
       </c>
       <c r="N91">
-        <v>-50.1294432</v>
+        <v>-51.010392</v>
       </c>
       <c r="O91">
-        <v>-15.03883296</v>
+        <v>-15.3031176</v>
       </c>
       <c r="P91">
-        <v>-35.09061024</v>
+        <v>-35.7072744</v>
       </c>
       <c r="Q91">
-        <v>-6.990610240000002</v>
+        <v>-7.607274400000001</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.7442340899231735</v>
+        <v>0.8140774989154911</v>
       </c>
       <c r="T91">
-        <v>5.982635361730463</v>
+        <v>6.580898897903511</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.1081890216140199</v>
+        <v>0.1069869213738642</v>
       </c>
       <c r="W91">
-        <v>0.2102890287034141</v>
+        <v>0.2105724839400429</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3606300720467331</v>
+        <v>0.356623071246214</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2709229854375876</v>
+        <v>0.2728229854375877</v>
       </c>
       <c r="C92">
-        <v>-188.6670391222159</v>
+        <v>-193.5704831374417</v>
       </c>
       <c r="D92">
-        <v>139.4929608777841</v>
+        <v>138.3255168625583</v>
       </c>
       <c r="E92">
-        <v>227.44</v>
+        <v>231.176</v>
       </c>
       <c r="F92">
-        <v>336.24</v>
+        <v>339.9760000000001</v>
       </c>
       <c r="G92">
         <v>8.08</v>
@@ -8831,37 +8831,37 @@
         <v>28.275</v>
       </c>
       <c r="M92">
-        <v>79.285392</v>
+        <v>80.16634080000001</v>
       </c>
       <c r="N92">
-        <v>-51.010392</v>
+        <v>-51.89134080000002</v>
       </c>
       <c r="O92">
-        <v>-15.3031176</v>
+        <v>-15.56740224</v>
       </c>
       <c r="P92">
-        <v>-35.7072744</v>
+        <v>-36.32393856000002</v>
       </c>
       <c r="Q92">
-        <v>-7.607274400000001</v>
+        <v>-8.223938560000015</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.8140774989154911</v>
+        <v>0.8994416654616568</v>
       </c>
       <c r="T92">
-        <v>6.580898897903511</v>
+        <v>7.312109886559456</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.1069869213738642</v>
+        <v>0.1058112409192063</v>
       </c>
       <c r="W92">
-        <v>0.2105724839400429</v>
+        <v>0.2108497093912511</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.356623071246214</v>
+        <v>0.3527041363973543</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2728229854375877</v>
+        <v>0.2747229854375877</v>
       </c>
       <c r="C93">
-        <v>-193.5704831374417</v>
+        <v>-198.4545482019283</v>
       </c>
       <c r="D93">
-        <v>138.3255168625583</v>
+        <v>137.1774517980718</v>
       </c>
       <c r="E93">
-        <v>231.176</v>
+        <v>234.912</v>
       </c>
       <c r="F93">
-        <v>339.9760000000001</v>
+        <v>343.712</v>
       </c>
       <c r="G93">
         <v>8.08</v>
@@ -8913,37 +8913,37 @@
         <v>28.275</v>
       </c>
       <c r="M93">
-        <v>80.16634080000001</v>
+        <v>81.04728960000001</v>
       </c>
       <c r="N93">
-        <v>-51.89134080000002</v>
+        <v>-52.77228960000001</v>
       </c>
       <c r="O93">
-        <v>-15.56740224</v>
+        <v>-15.83168688</v>
       </c>
       <c r="P93">
-        <v>-36.32393856000002</v>
+        <v>-36.94060272000002</v>
       </c>
       <c r="Q93">
-        <v>-8.223938560000015</v>
+        <v>-8.840602720000014</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.8994416654616568</v>
+        <v>1.006146873644364</v>
       </c>
       <c r="T93">
-        <v>7.312109886559456</v>
+        <v>8.22612362237939</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.1058112409192063</v>
+        <v>0.1046611187353019</v>
       </c>
       <c r="W93">
-        <v>0.2108497093912511</v>
+        <v>0.2111209082022158</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3527041363973543</v>
+        <v>0.3488703957843396</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2747229854375877</v>
+        <v>0.2766229854375876</v>
       </c>
       <c r="C94">
-        <v>-198.4545482019283</v>
+        <v>-203.3197128642873</v>
       </c>
       <c r="D94">
-        <v>137.1774517980718</v>
+        <v>136.0482871357127</v>
       </c>
       <c r="E94">
-        <v>234.912</v>
+        <v>238.648</v>
       </c>
       <c r="F94">
-        <v>343.712</v>
+        <v>347.448</v>
       </c>
       <c r="G94">
         <v>8.08</v>
@@ -8995,37 +8995,37 @@
         <v>28.275</v>
       </c>
       <c r="M94">
-        <v>81.04728960000001</v>
+        <v>81.92823840000001</v>
       </c>
       <c r="N94">
-        <v>-52.77228960000001</v>
+        <v>-53.65323840000001</v>
       </c>
       <c r="O94">
-        <v>-15.83168688</v>
+        <v>-16.09597152</v>
       </c>
       <c r="P94">
-        <v>-36.94060272000002</v>
+        <v>-37.55726688000001</v>
       </c>
       <c r="Q94">
-        <v>-8.840602720000014</v>
+        <v>-9.457266880000013</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>1.006146873644364</v>
+        <v>1.143339284164988</v>
       </c>
       <c r="T94">
-        <v>8.22612362237939</v>
+        <v>9.401284139862161</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.1046611187353019</v>
+        <v>0.103535730361804</v>
       </c>
       <c r="W94">
-        <v>0.2111209082022158</v>
+        <v>0.2113862747806866</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3488703957843396</v>
+        <v>0.3451191012060134</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2766229854375876</v>
+        <v>0.2785229854375876</v>
       </c>
       <c r="C95">
-        <v>-203.3197128642873</v>
+        <v>-208.1664400452394</v>
       </c>
       <c r="D95">
-        <v>136.0482871357127</v>
+        <v>134.9375599547606</v>
       </c>
       <c r="E95">
-        <v>238.648</v>
+        <v>242.384</v>
       </c>
       <c r="F95">
-        <v>347.448</v>
+        <v>351.184</v>
       </c>
       <c r="G95">
         <v>8.08</v>
@@ -9077,37 +9077,37 @@
         <v>28.275</v>
       </c>
       <c r="M95">
-        <v>81.92823840000001</v>
+        <v>82.80918720000001</v>
       </c>
       <c r="N95">
-        <v>-53.65323840000001</v>
+        <v>-54.53418720000001</v>
       </c>
       <c r="O95">
-        <v>-16.09597152</v>
+        <v>-16.36025616</v>
       </c>
       <c r="P95">
-        <v>-37.55726688000001</v>
+        <v>-38.17393104000001</v>
       </c>
       <c r="Q95">
-        <v>-9.457266880000013</v>
+        <v>-10.07393104000001</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>1.143339284164988</v>
+        <v>1.326262498192486</v>
       </c>
       <c r="T95">
-        <v>9.401284139862161</v>
+        <v>10.96816482983919</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.103535730361804</v>
+        <v>0.1024342864217848</v>
       </c>
       <c r="W95">
-        <v>0.2113862747806866</v>
+        <v>0.2116459952617431</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3451191012060134</v>
+        <v>0.3414476214059494</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2785229854375876</v>
+        <v>0.2804229854375877</v>
       </c>
       <c r="C96">
-        <v>-208.1664400452394</v>
+        <v>-212.9951776703953</v>
       </c>
       <c r="D96">
-        <v>134.9375599547606</v>
+        <v>133.8448223296047</v>
       </c>
       <c r="E96">
-        <v>242.384</v>
+        <v>246.1200000000001</v>
       </c>
       <c r="F96">
-        <v>351.184</v>
+        <v>354.9200000000001</v>
       </c>
       <c r="G96">
         <v>8.08</v>
@@ -9159,37 +9159,37 @@
         <v>28.275</v>
       </c>
       <c r="M96">
-        <v>82.80918720000001</v>
+        <v>83.69013600000002</v>
       </c>
       <c r="N96">
-        <v>-54.53418720000001</v>
+        <v>-55.41513600000003</v>
       </c>
       <c r="O96">
-        <v>-16.36025616</v>
+        <v>-16.62454080000001</v>
       </c>
       <c r="P96">
-        <v>-38.17393104000001</v>
+        <v>-38.79059520000002</v>
       </c>
       <c r="Q96">
-        <v>-10.07393104000001</v>
+        <v>-10.69059520000002</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.326262498192486</v>
+        <v>1.582354997830984</v>
       </c>
       <c r="T96">
-        <v>10.96816482983919</v>
+        <v>13.16179779580704</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.1024342864217848</v>
+        <v>0.1013560307752397</v>
       </c>
       <c r="W96">
-        <v>0.2116459952617431</v>
+        <v>0.2119002479431985</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3414476214059494</v>
+        <v>0.3378534359174657</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2804229854375877</v>
+        <v>0.2823229854375877</v>
       </c>
       <c r="C97">
-        <v>-212.9951776703953</v>
+        <v>-217.8063592725375</v>
       </c>
       <c r="D97">
-        <v>133.8448223296047</v>
+        <v>132.7696407274626</v>
       </c>
       <c r="E97">
-        <v>246.1200000000001</v>
+        <v>249.8560000000001</v>
       </c>
       <c r="F97">
-        <v>354.9200000000001</v>
+        <v>358.6560000000001</v>
       </c>
       <c r="G97">
         <v>8.08</v>
@@ -9241,37 +9241,37 @@
         <v>28.275</v>
       </c>
       <c r="M97">
-        <v>83.69013600000002</v>
+        <v>84.57108480000002</v>
       </c>
       <c r="N97">
-        <v>-55.41513600000003</v>
+        <v>-56.29608480000002</v>
       </c>
       <c r="O97">
-        <v>-16.62454080000001</v>
+        <v>-16.88882544000001</v>
       </c>
       <c r="P97">
-        <v>-38.79059520000002</v>
+        <v>-39.40725936000002</v>
       </c>
       <c r="Q97">
-        <v>-10.69059520000002</v>
+        <v>-11.30725936000002</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.582354997830984</v>
+        <v>1.966493747288731</v>
       </c>
       <c r="T97">
-        <v>13.16179779580704</v>
+        <v>16.4522472447588</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.1013560307752397</v>
+        <v>0.1003002387879976</v>
       </c>
       <c r="W97">
-        <v>0.2119002479431985</v>
+        <v>0.2121492036937902</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3378534359174657</v>
+        <v>0.3343341292933254</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2823229854375877</v>
+        <v>0.2842229854375876</v>
       </c>
       <c r="C98">
-        <v>-217.8063592725374</v>
+        <v>-222.6004045651052</v>
       </c>
       <c r="D98">
-        <v>132.7696407274626</v>
+        <v>131.7115954348948</v>
       </c>
       <c r="E98">
-        <v>249.856</v>
+        <v>253.592</v>
       </c>
       <c r="F98">
-        <v>358.656</v>
+        <v>362.392</v>
       </c>
       <c r="G98">
         <v>8.08</v>
@@ -9323,37 +9323,37 @@
         <v>28.275</v>
       </c>
       <c r="M98">
-        <v>84.57108480000001</v>
+        <v>85.45203360000001</v>
       </c>
       <c r="N98">
-        <v>-56.29608480000001</v>
+        <v>-57.17703360000001</v>
       </c>
       <c r="O98">
-        <v>-16.88882544</v>
+        <v>-17.15311008</v>
       </c>
       <c r="P98">
-        <v>-39.40725936000001</v>
+        <v>-40.02392352000001</v>
       </c>
       <c r="Q98">
-        <v>-11.30725936000001</v>
+        <v>-11.92392352000001</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.966493747288726</v>
+        <v>2.606724996384968</v>
       </c>
       <c r="T98">
-        <v>16.45224724475876</v>
+        <v>21.93632965967835</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.1003002387879977</v>
+        <v>0.09926621570770902</v>
       </c>
       <c r="W98">
-        <v>0.2121492036937902</v>
+        <v>0.2123930263361222</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3343341292933255</v>
+        <v>0.3308873856923634</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2842229854375876</v>
+        <v>0.2861229854375876</v>
       </c>
       <c r="C99">
-        <v>-222.6004045651052</v>
+        <v>-227.3777199884744</v>
       </c>
       <c r="D99">
-        <v>131.7115954348948</v>
+        <v>130.6702800115256</v>
       </c>
       <c r="E99">
-        <v>253.592</v>
+        <v>257.328</v>
       </c>
       <c r="F99">
-        <v>362.392</v>
+        <v>366.128</v>
       </c>
       <c r="G99">
         <v>8.08</v>
@@ -9405,37 +9405,37 @@
         <v>28.275</v>
       </c>
       <c r="M99">
-        <v>85.45203360000001</v>
+        <v>86.33298240000002</v>
       </c>
       <c r="N99">
-        <v>-57.17703360000001</v>
+        <v>-58.05798240000002</v>
       </c>
       <c r="O99">
-        <v>-17.15311008</v>
+        <v>-17.41739472</v>
       </c>
       <c r="P99">
-        <v>-40.02392352000001</v>
+        <v>-40.64058768000002</v>
       </c>
       <c r="Q99">
-        <v>-11.92392352000001</v>
+        <v>-12.54058768000002</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>2.606724996384968</v>
+        <v>3.887187494577451</v>
       </c>
       <c r="T99">
-        <v>21.93632965967835</v>
+        <v>32.90449448951752</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.09926621570770902</v>
+        <v>0.09825329513926298</v>
       </c>
       <c r="W99">
-        <v>0.2123930263361222</v>
+        <v>0.2126318730061618</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3308873856923634</v>
+        <v>0.3275109837975433</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2861229854375876</v>
+        <v>0.2880229854375876</v>
       </c>
       <c r="C100">
-        <v>-227.3777199884744</v>
+        <v>-232.1386992305285</v>
       </c>
       <c r="D100">
-        <v>130.6702800115256</v>
+        <v>129.6453007694715</v>
       </c>
       <c r="E100">
-        <v>257.328</v>
+        <v>261.064</v>
       </c>
       <c r="F100">
-        <v>366.128</v>
+        <v>369.864</v>
       </c>
       <c r="G100">
         <v>8.08</v>
@@ -9487,37 +9487,37 @@
         <v>28.275</v>
       </c>
       <c r="M100">
-        <v>86.33298240000002</v>
+        <v>87.2139312</v>
       </c>
       <c r="N100">
-        <v>-58.05798240000002</v>
+        <v>-58.93893120000001</v>
       </c>
       <c r="O100">
-        <v>-17.41739472</v>
+        <v>-17.68167936</v>
       </c>
       <c r="P100">
-        <v>-40.64058768000002</v>
+        <v>-41.25725184000001</v>
       </c>
       <c r="Q100">
-        <v>-12.54058768000002</v>
+        <v>-13.15725184000001</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>3.887187494577451</v>
+        <v>7.728574989154901</v>
       </c>
       <c r="T100">
-        <v>32.90449448951752</v>
+        <v>65.80898897903502</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.09825329513926298</v>
+        <v>0.09726083761260379</v>
       </c>
       <c r="W100">
-        <v>0.2126318730061618</v>
+        <v>0.212865894490948</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3275109837975433</v>
+        <v>0.3242027920420126</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2880229854375876</v>
-      </c>
-      <c r="C101">
-        <v>-232.1386992305285</v>
-      </c>
-      <c r="D101">
-        <v>129.6453007694715</v>
-      </c>
-      <c r="E101">
-        <v>261.064</v>
-      </c>
-      <c r="F101">
-        <v>369.864</v>
-      </c>
-      <c r="G101">
-        <v>8.08</v>
-      </c>
-      <c r="H101">
-        <v>264.8</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>56.375</v>
-      </c>
-      <c r="K101">
-        <v>28.1</v>
-      </c>
-      <c r="L101">
-        <v>28.275</v>
-      </c>
-      <c r="M101">
-        <v>87.2139312</v>
-      </c>
-      <c r="N101">
-        <v>-58.93893120000001</v>
-      </c>
-      <c r="O101">
-        <v>-17.68167936</v>
-      </c>
-      <c r="P101">
-        <v>-41.25725184000001</v>
-      </c>
-      <c r="Q101">
-        <v>-13.15725184000001</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>7.728574989154901</v>
-      </c>
-      <c r="T101">
-        <v>65.80898897903502</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.09726083761260379</v>
-      </c>
-      <c r="W101">
-        <v>0.212865894490948</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.3242027920420126</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
